--- a/Globos.xlsx
+++ b/Globos.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Globos" sheetId="1" r:id="rId4"/>
+    <sheet name="Globos" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Globos!$A$1:$F$17</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Globos!$A$1:$F$17</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataSignature="AMtx7mj3AwAVwGWPr0Y0WXT7Ws0S79kXAw=="/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -20,78 +25,94 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="17">
   <si>
-    <t>Orden</t>
+    <t xml:space="preserve">Orden</t>
   </si>
   <si>
-    <t>Color</t>
+    <t xml:space="preserve">Color</t>
   </si>
   <si>
-    <t>Tamanio</t>
+    <t xml:space="preserve">Volumen</t>
   </si>
   <si>
-    <t>Se estira?</t>
+    <t xml:space="preserve">Estira</t>
   </si>
   <si>
-    <t>Edad</t>
+    <t xml:space="preserve">Edad</t>
   </si>
   <si>
-    <t>Inflado?</t>
+    <t xml:space="preserve">Inflado?</t>
   </si>
   <si>
-    <t>Amarillo</t>
+    <t xml:space="preserve">Amarillo</t>
   </si>
   <si>
-    <t>Chico</t>
+    <t xml:space="preserve">Chico</t>
   </si>
   <si>
-    <t>Si</t>
+    <t xml:space="preserve">Si</t>
   </si>
   <si>
-    <t>Adulto</t>
+    <t xml:space="preserve">Adulto</t>
   </si>
   <si>
-    <t>Inflado</t>
+    <t xml:space="preserve">Inflado</t>
   </si>
   <si>
-    <t>Niño</t>
+    <t xml:space="preserve">Niño</t>
   </si>
   <si>
-    <t>Grande</t>
+    <t xml:space="preserve">Grande</t>
   </si>
   <si>
-    <t>Rojo</t>
+    <t xml:space="preserve">Rojo</t>
   </si>
   <si>
-    <t>Mediano</t>
+    <t xml:space="preserve">Mediano</t>
   </si>
   <si>
-    <t>No</t>
+    <t xml:space="preserve">No</t>
   </si>
   <si>
-    <t>No Inflado</t>
+    <t xml:space="preserve">No Inflado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11.0"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -99,58 +120,172 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6D9F1"/>
-        <bgColor rgb="FFC6D9F1"/>
+        <bgColor rgb="FFC0C0C0"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6D9F1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFC6D9F1"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -161,94 +296,90 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Calibri" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -256,33 +387,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -295,13 +417,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -311,15 +427,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -327,7 +441,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -335,11 +448,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -348,17 +461,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <dimension ref="A1:F1000"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col customWidth="1" min="1" max="6" width="11.43"/>
-    <col customWidth="1" min="7" max="26" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="1" style="0" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="7" style="0" width="10.57"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -378,9 +492,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>6</v>
@@ -398,9 +512,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>2.0</v>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -418,9 +532,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>5.0</v>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
@@ -438,9 +552,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>6.0</v>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>6</v>
@@ -458,9 +572,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>9.0</v>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
@@ -478,9 +592,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>13.0</v>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
@@ -498,9 +612,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>3.0</v>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
@@ -518,9 +632,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>4.0</v>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>6</v>
@@ -538,9 +652,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>7.0</v>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
@@ -558,9 +672,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>8.0</v>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
@@ -578,9 +692,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>10.0</v>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>13</v>
@@ -598,9 +712,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>11.0</v>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>13</v>
@@ -618,9 +732,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>12.0</v>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>13</v>
@@ -638,9 +752,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>14.0</v>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>13</v>
@@ -658,9 +772,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>15.0</v>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>13</v>
@@ -678,9 +792,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>16.0</v>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>13</v>
@@ -698,7 +812,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -706,7 +820,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -714,7 +828,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -722,7 +836,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -730,7 +844,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -738,7 +852,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -746,7 +860,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -754,7 +868,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -762,7 +876,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -770,7 +884,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -778,7 +892,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -786,7 +900,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -794,7 +908,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -802,7 +916,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -810,7 +924,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -818,7 +932,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -826,7 +940,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -834,7 +948,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -842,7 +956,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -850,7 +964,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -858,7 +972,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -866,7 +980,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -874,7 +988,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -882,7 +996,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -890,7 +1004,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -898,7 +1012,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -906,7 +1020,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -914,7 +1028,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -922,7 +1036,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -930,7 +1044,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -938,7 +1052,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -946,7 +1060,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -954,7 +1068,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -962,7 +1076,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -970,7 +1084,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -978,7 +1092,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -986,7 +1100,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -994,7 +1108,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1002,7 +1116,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1010,7 +1124,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1018,7 +1132,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -1026,7 +1140,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -1034,7 +1148,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -1042,7 +1156,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -1050,7 +1164,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -1058,7 +1172,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -1066,7 +1180,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -1074,7 +1188,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -1082,7 +1196,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -1090,7 +1204,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -1098,7 +1212,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -1106,7 +1220,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -1114,7 +1228,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -1122,7 +1236,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -1130,7 +1244,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -1138,7 +1252,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -1146,7 +1260,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -1154,7 +1268,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -1162,7 +1276,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -1170,7 +1284,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -1178,7 +1292,7 @@
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -1186,7 +1300,7 @@
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -1194,7 +1308,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -1202,7 +1316,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -1210,7 +1324,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -1218,7 +1332,7 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -1226,7 +1340,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -1234,7 +1348,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -1242,7 +1356,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -1250,7 +1364,7 @@
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -1258,7 +1372,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -1266,7 +1380,7 @@
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -1274,7 +1388,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -1282,7 +1396,7 @@
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -1290,7 +1404,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -1298,7 +1412,7 @@
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -1306,7 +1420,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -1314,7 +1428,7 @@
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -1322,7 +1436,7 @@
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -1330,7 +1444,7 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -1338,7 +1452,7 @@
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -1346,7 +1460,7 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -1354,7 +1468,7 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -1362,7 +1476,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -1370,7 +1484,7 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -1378,7 +1492,7 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -1386,7 +1500,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -1394,7 +1508,7 @@
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -1402,7 +1516,7 @@
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -1410,7 +1524,7 @@
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -1418,7 +1532,7 @@
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -1426,7 +1540,7 @@
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -1434,7 +1548,7 @@
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -1442,7 +1556,7 @@
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -1450,7 +1564,7 @@
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -1458,7 +1572,7 @@
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -1466,7 +1580,7 @@
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -1474,7 +1588,7 @@
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -1482,7 +1596,7 @@
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -1490,7 +1604,7 @@
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -1498,7 +1612,7 @@
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -1506,7 +1620,7 @@
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -1514,7 +1628,7 @@
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -1522,7 +1636,7 @@
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -1530,7 +1644,7 @@
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -1538,7 +1652,7 @@
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -1546,7 +1660,7 @@
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -1554,7 +1668,7 @@
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -1562,7 +1676,7 @@
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -1570,7 +1684,7 @@
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -1578,7 +1692,7 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -1586,7 +1700,7 @@
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -1594,7 +1708,7 @@
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -1602,7 +1716,7 @@
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -1610,7 +1724,7 @@
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -1618,7 +1732,7 @@
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -1626,7 +1740,7 @@
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -1634,7 +1748,7 @@
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -1642,7 +1756,7 @@
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -1650,7 +1764,7 @@
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -1658,7 +1772,7 @@
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -1666,7 +1780,7 @@
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -1674,7 +1788,7 @@
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -1682,7 +1796,7 @@
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -1690,7 +1804,7 @@
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -1698,7 +1812,7 @@
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -1706,7 +1820,7 @@
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -1714,7 +1828,7 @@
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -1722,7 +1836,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -1730,7 +1844,7 @@
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -1738,7 +1852,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -1746,7 +1860,7 @@
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -1754,7 +1868,7 @@
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -1762,7 +1876,7 @@
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -1770,7 +1884,7 @@
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -1778,7 +1892,7 @@
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -1786,7 +1900,7 @@
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -1794,7 +1908,7 @@
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -1802,7 +1916,7 @@
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -1810,7 +1924,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -1818,7 +1932,7 @@
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -1826,7 +1940,7 @@
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -1834,7 +1948,7 @@
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -1842,7 +1956,7 @@
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -1850,7 +1964,7 @@
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -1858,7 +1972,7 @@
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -1866,7 +1980,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -1874,7 +1988,7 @@
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -1882,7 +1996,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -1890,7 +2004,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -1898,7 +2012,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -1906,7 +2020,7 @@
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -1914,7 +2028,7 @@
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -1922,7 +2036,7 @@
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -1930,7 +2044,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -1938,7 +2052,7 @@
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -1946,7 +2060,7 @@
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -1954,7 +2068,7 @@
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -1962,7 +2076,7 @@
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -1970,7 +2084,7 @@
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -1978,7 +2092,7 @@
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -1986,7 +2100,7 @@
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -1994,7 +2108,7 @@
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -2002,7 +2116,7 @@
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -2010,7 +2124,7 @@
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -2018,7 +2132,7 @@
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -2026,7 +2140,7 @@
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -2034,7 +2148,7 @@
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -2042,7 +2156,7 @@
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -2050,7 +2164,7 @@
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -2058,7 +2172,7 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -2066,7 +2180,7 @@
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -2074,7 +2188,7 @@
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -2082,7 +2196,7 @@
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -2090,7 +2204,7 @@
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -2098,7 +2212,7 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -2106,7 +2220,7 @@
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -2114,7 +2228,7 @@
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -2122,7 +2236,7 @@
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -2130,7 +2244,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -2138,7 +2252,7 @@
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -2146,7 +2260,7 @@
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -2154,7 +2268,7 @@
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -2162,7 +2276,7 @@
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -2170,7 +2284,7 @@
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -2178,7 +2292,7 @@
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -2186,7 +2300,7 @@
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -2194,7 +2308,7 @@
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -2202,7 +2316,7 @@
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -2210,7 +2324,7 @@
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -2218,7 +2332,7 @@
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -2226,7 +2340,7 @@
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -2234,7 +2348,7 @@
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -2242,7 +2356,7 @@
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -2250,7 +2364,7 @@
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -2258,7 +2372,7 @@
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -2266,7 +2380,7 @@
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -2274,7 +2388,7 @@
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -2282,7 +2396,7 @@
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -2290,7 +2404,7 @@
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -2298,7 +2412,7 @@
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -2306,7 +2420,7 @@
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -2314,7 +2428,7 @@
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -2322,7 +2436,7 @@
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -2330,7 +2444,7 @@
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -2338,7 +2452,7 @@
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -2346,7 +2460,7 @@
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -2354,7 +2468,7 @@
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -2362,7 +2476,7 @@
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -2370,7 +2484,7 @@
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -2378,7 +2492,7 @@
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -2386,7 +2500,7 @@
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -2394,7 +2508,7 @@
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -2402,7 +2516,7 @@
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -2410,7 +2524,7 @@
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -2418,7 +2532,7 @@
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -2426,7 +2540,7 @@
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -2434,7 +2548,7 @@
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -2442,7 +2556,7 @@
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -2450,7 +2564,7 @@
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -2458,7 +2572,7 @@
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -2466,7 +2580,7 @@
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -2474,7 +2588,7 @@
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -2482,7 +2596,7 @@
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -2490,7 +2604,7 @@
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -2498,7 +2612,7 @@
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -2506,7 +2620,7 @@
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -2514,7 +2628,7 @@
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -2522,7 +2636,7 @@
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -2530,7 +2644,7 @@
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -2538,7 +2652,7 @@
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -2546,7 +2660,7 @@
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -2554,7 +2668,7 @@
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -2562,7 +2676,7 @@
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1">
+    <row r="251" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -2570,7 +2684,7 @@
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
     </row>
-    <row r="252" ht="15.75" customHeight="1">
+    <row r="252" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -2578,7 +2692,7 @@
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
     </row>
-    <row r="253" ht="15.75" customHeight="1">
+    <row r="253" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -2586,7 +2700,7 @@
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
     </row>
-    <row r="254" ht="15.75" customHeight="1">
+    <row r="254" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -2594,7 +2708,7 @@
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
     </row>
-    <row r="255" ht="15.75" customHeight="1">
+    <row r="255" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -2602,7 +2716,7 @@
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
     </row>
-    <row r="256" ht="15.75" customHeight="1">
+    <row r="256" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -2610,7 +2724,7 @@
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
     </row>
-    <row r="257" ht="15.75" customHeight="1">
+    <row r="257" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -2618,7 +2732,7 @@
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -2626,7 +2740,7 @@
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -2634,7 +2748,7 @@
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
     </row>
-    <row r="260" ht="15.75" customHeight="1">
+    <row r="260" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -2642,7 +2756,7 @@
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
     </row>
-    <row r="261" ht="15.75" customHeight="1">
+    <row r="261" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -2650,7 +2764,7 @@
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
     </row>
-    <row r="262" ht="15.75" customHeight="1">
+    <row r="262" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -2658,7 +2772,7 @@
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
     </row>
-    <row r="263" ht="15.75" customHeight="1">
+    <row r="263" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -2666,7 +2780,7 @@
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
     </row>
-    <row r="264" ht="15.75" customHeight="1">
+    <row r="264" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -2674,7 +2788,7 @@
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
     </row>
-    <row r="265" ht="15.75" customHeight="1">
+    <row r="265" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -2682,7 +2796,7 @@
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
     </row>
-    <row r="266" ht="15.75" customHeight="1">
+    <row r="266" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -2690,7 +2804,7 @@
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
     </row>
-    <row r="267" ht="15.75" customHeight="1">
+    <row r="267" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -2698,7 +2812,7 @@
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
     </row>
-    <row r="268" ht="15.75" customHeight="1">
+    <row r="268" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -2706,7 +2820,7 @@
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
     </row>
-    <row r="269" ht="15.75" customHeight="1">
+    <row r="269" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -2714,7 +2828,7 @@
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
     </row>
-    <row r="270" ht="15.75" customHeight="1">
+    <row r="270" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -2722,7 +2836,7 @@
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
     </row>
-    <row r="271" ht="15.75" customHeight="1">
+    <row r="271" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -2730,7 +2844,7 @@
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
     </row>
-    <row r="272" ht="15.75" customHeight="1">
+    <row r="272" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -2738,7 +2852,7 @@
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
     </row>
-    <row r="273" ht="15.75" customHeight="1">
+    <row r="273" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -2746,7 +2860,7 @@
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
     </row>
-    <row r="274" ht="15.75" customHeight="1">
+    <row r="274" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -2754,7 +2868,7 @@
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
     </row>
-    <row r="275" ht="15.75" customHeight="1">
+    <row r="275" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -2762,7 +2876,7 @@
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
     </row>
-    <row r="276" ht="15.75" customHeight="1">
+    <row r="276" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -2770,7 +2884,7 @@
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
     </row>
-    <row r="277" ht="15.75" customHeight="1">
+    <row r="277" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -2778,7 +2892,7 @@
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
     </row>
-    <row r="278" ht="15.75" customHeight="1">
+    <row r="278" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -2786,7 +2900,7 @@
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
     </row>
-    <row r="279" ht="15.75" customHeight="1">
+    <row r="279" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -2794,7 +2908,7 @@
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
     </row>
-    <row r="280" ht="15.75" customHeight="1">
+    <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -2802,7 +2916,7 @@
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
     </row>
-    <row r="281" ht="15.75" customHeight="1">
+    <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -2810,7 +2924,7 @@
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
     </row>
-    <row r="282" ht="15.75" customHeight="1">
+    <row r="282" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -2818,7 +2932,7 @@
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
     </row>
-    <row r="283" ht="15.75" customHeight="1">
+    <row r="283" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -2826,7 +2940,7 @@
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
     </row>
-    <row r="284" ht="15.75" customHeight="1">
+    <row r="284" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -2834,7 +2948,7 @@
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
     </row>
-    <row r="285" ht="15.75" customHeight="1">
+    <row r="285" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -2842,7 +2956,7 @@
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
     </row>
-    <row r="286" ht="15.75" customHeight="1">
+    <row r="286" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -2850,7 +2964,7 @@
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
     </row>
-    <row r="287" ht="15.75" customHeight="1">
+    <row r="287" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -2858,7 +2972,7 @@
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
     </row>
-    <row r="288" ht="15.75" customHeight="1">
+    <row r="288" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -2866,7 +2980,7 @@
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
     </row>
-    <row r="289" ht="15.75" customHeight="1">
+    <row r="289" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -2874,7 +2988,7 @@
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
     </row>
-    <row r="290" ht="15.75" customHeight="1">
+    <row r="290" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -2882,7 +2996,7 @@
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
     </row>
-    <row r="291" ht="15.75" customHeight="1">
+    <row r="291" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -2890,7 +3004,7 @@
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
     </row>
-    <row r="292" ht="15.75" customHeight="1">
+    <row r="292" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -2898,7 +3012,7 @@
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
     </row>
-    <row r="293" ht="15.75" customHeight="1">
+    <row r="293" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -2906,7 +3020,7 @@
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
     </row>
-    <row r="294" ht="15.75" customHeight="1">
+    <row r="294" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -2914,7 +3028,7 @@
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
     </row>
-    <row r="295" ht="15.75" customHeight="1">
+    <row r="295" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -2922,7 +3036,7 @@
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
     </row>
-    <row r="296" ht="15.75" customHeight="1">
+    <row r="296" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -2930,7 +3044,7 @@
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
     </row>
-    <row r="297" ht="15.75" customHeight="1">
+    <row r="297" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -2938,7 +3052,7 @@
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
     </row>
-    <row r="298" ht="15.75" customHeight="1">
+    <row r="298" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -2946,7 +3060,7 @@
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
     </row>
-    <row r="299" ht="15.75" customHeight="1">
+    <row r="299" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -2954,7 +3068,7 @@
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
     </row>
-    <row r="300" ht="15.75" customHeight="1">
+    <row r="300" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -2962,7 +3076,7 @@
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
     </row>
-    <row r="301" ht="15.75" customHeight="1">
+    <row r="301" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -2970,7 +3084,7 @@
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
     </row>
-    <row r="302" ht="15.75" customHeight="1">
+    <row r="302" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -2978,7 +3092,7 @@
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
     </row>
-    <row r="303" ht="15.75" customHeight="1">
+    <row r="303" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -2986,7 +3100,7 @@
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
     </row>
-    <row r="304" ht="15.75" customHeight="1">
+    <row r="304" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -2994,7 +3108,7 @@
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
     </row>
-    <row r="305" ht="15.75" customHeight="1">
+    <row r="305" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -3002,7 +3116,7 @@
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
     </row>
-    <row r="306" ht="15.75" customHeight="1">
+    <row r="306" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -3010,7 +3124,7 @@
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
     </row>
-    <row r="307" ht="15.75" customHeight="1">
+    <row r="307" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -3018,7 +3132,7 @@
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
     </row>
-    <row r="308" ht="15.75" customHeight="1">
+    <row r="308" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -3026,7 +3140,7 @@
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
     </row>
-    <row r="309" ht="15.75" customHeight="1">
+    <row r="309" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -3034,7 +3148,7 @@
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
     </row>
-    <row r="310" ht="15.75" customHeight="1">
+    <row r="310" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -3042,7 +3156,7 @@
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
     </row>
-    <row r="311" ht="15.75" customHeight="1">
+    <row r="311" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -3050,7 +3164,7 @@
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
     </row>
-    <row r="312" ht="15.75" customHeight="1">
+    <row r="312" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -3058,7 +3172,7 @@
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
     </row>
-    <row r="313" ht="15.75" customHeight="1">
+    <row r="313" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -3066,7 +3180,7 @@
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
     </row>
-    <row r="314" ht="15.75" customHeight="1">
+    <row r="314" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -3074,7 +3188,7 @@
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
     </row>
-    <row r="315" ht="15.75" customHeight="1">
+    <row r="315" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -3082,7 +3196,7 @@
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
     </row>
-    <row r="316" ht="15.75" customHeight="1">
+    <row r="316" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -3090,7 +3204,7 @@
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
     </row>
-    <row r="317" ht="15.75" customHeight="1">
+    <row r="317" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -3098,7 +3212,7 @@
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
     </row>
-    <row r="318" ht="15.75" customHeight="1">
+    <row r="318" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -3106,7 +3220,7 @@
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
     </row>
-    <row r="319" ht="15.75" customHeight="1">
+    <row r="319" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -3114,7 +3228,7 @@
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
     </row>
-    <row r="320" ht="15.75" customHeight="1">
+    <row r="320" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -3122,7 +3236,7 @@
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
     </row>
-    <row r="321" ht="15.75" customHeight="1">
+    <row r="321" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -3130,7 +3244,7 @@
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
     </row>
-    <row r="322" ht="15.75" customHeight="1">
+    <row r="322" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -3138,7 +3252,7 @@
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
     </row>
-    <row r="323" ht="15.75" customHeight="1">
+    <row r="323" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -3146,7 +3260,7 @@
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
     </row>
-    <row r="324" ht="15.75" customHeight="1">
+    <row r="324" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -3154,7 +3268,7 @@
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
     </row>
-    <row r="325" ht="15.75" customHeight="1">
+    <row r="325" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -3162,7 +3276,7 @@
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
     </row>
-    <row r="326" ht="15.75" customHeight="1">
+    <row r="326" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -3170,7 +3284,7 @@
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
     </row>
-    <row r="327" ht="15.75" customHeight="1">
+    <row r="327" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -3178,7 +3292,7 @@
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
     </row>
-    <row r="328" ht="15.75" customHeight="1">
+    <row r="328" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -3186,7 +3300,7 @@
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
     </row>
-    <row r="329" ht="15.75" customHeight="1">
+    <row r="329" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -3194,7 +3308,7 @@
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
     </row>
-    <row r="330" ht="15.75" customHeight="1">
+    <row r="330" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -3202,7 +3316,7 @@
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
     </row>
-    <row r="331" ht="15.75" customHeight="1">
+    <row r="331" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -3210,7 +3324,7 @@
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
     </row>
-    <row r="332" ht="15.75" customHeight="1">
+    <row r="332" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -3218,7 +3332,7 @@
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
     </row>
-    <row r="333" ht="15.75" customHeight="1">
+    <row r="333" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -3226,7 +3340,7 @@
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
     </row>
-    <row r="334" ht="15.75" customHeight="1">
+    <row r="334" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -3234,7 +3348,7 @@
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
     </row>
-    <row r="335" ht="15.75" customHeight="1">
+    <row r="335" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -3242,7 +3356,7 @@
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
     </row>
-    <row r="336" ht="15.75" customHeight="1">
+    <row r="336" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -3250,7 +3364,7 @@
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
     </row>
-    <row r="337" ht="15.75" customHeight="1">
+    <row r="337" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -3258,7 +3372,7 @@
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
     </row>
-    <row r="338" ht="15.75" customHeight="1">
+    <row r="338" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -3266,7 +3380,7 @@
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
     </row>
-    <row r="339" ht="15.75" customHeight="1">
+    <row r="339" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -3274,7 +3388,7 @@
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
     </row>
-    <row r="340" ht="15.75" customHeight="1">
+    <row r="340" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -3282,7 +3396,7 @@
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
     </row>
-    <row r="341" ht="15.75" customHeight="1">
+    <row r="341" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -3290,7 +3404,7 @@
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
     </row>
-    <row r="342" ht="15.75" customHeight="1">
+    <row r="342" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -3298,7 +3412,7 @@
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
     </row>
-    <row r="343" ht="15.75" customHeight="1">
+    <row r="343" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -3306,7 +3420,7 @@
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
     </row>
-    <row r="344" ht="15.75" customHeight="1">
+    <row r="344" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -3314,7 +3428,7 @@
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
     </row>
-    <row r="345" ht="15.75" customHeight="1">
+    <row r="345" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -3322,7 +3436,7 @@
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
     </row>
-    <row r="346" ht="15.75" customHeight="1">
+    <row r="346" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -3330,7 +3444,7 @@
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
     </row>
-    <row r="347" ht="15.75" customHeight="1">
+    <row r="347" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -3338,7 +3452,7 @@
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
     </row>
-    <row r="348" ht="15.75" customHeight="1">
+    <row r="348" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -3346,7 +3460,7 @@
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
     </row>
-    <row r="349" ht="15.75" customHeight="1">
+    <row r="349" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -3354,7 +3468,7 @@
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
     </row>
-    <row r="350" ht="15.75" customHeight="1">
+    <row r="350" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -3362,7 +3476,7 @@
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
     </row>
-    <row r="351" ht="15.75" customHeight="1">
+    <row r="351" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -3370,7 +3484,7 @@
       <c r="E351" s="3"/>
       <c r="F351" s="3"/>
     </row>
-    <row r="352" ht="15.75" customHeight="1">
+    <row r="352" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -3378,7 +3492,7 @@
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
     </row>
-    <row r="353" ht="15.75" customHeight="1">
+    <row r="353" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -3386,7 +3500,7 @@
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
     </row>
-    <row r="354" ht="15.75" customHeight="1">
+    <row r="354" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -3394,7 +3508,7 @@
       <c r="E354" s="3"/>
       <c r="F354" s="3"/>
     </row>
-    <row r="355" ht="15.75" customHeight="1">
+    <row r="355" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -3402,7 +3516,7 @@
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
     </row>
-    <row r="356" ht="15.75" customHeight="1">
+    <row r="356" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -3410,7 +3524,7 @@
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
     </row>
-    <row r="357" ht="15.75" customHeight="1">
+    <row r="357" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -3418,7 +3532,7 @@
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
     </row>
-    <row r="358" ht="15.75" customHeight="1">
+    <row r="358" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -3426,7 +3540,7 @@
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
     </row>
-    <row r="359" ht="15.75" customHeight="1">
+    <row r="359" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -3434,7 +3548,7 @@
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
     </row>
-    <row r="360" ht="15.75" customHeight="1">
+    <row r="360" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -3442,7 +3556,7 @@
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
     </row>
-    <row r="361" ht="15.75" customHeight="1">
+    <row r="361" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -3450,7 +3564,7 @@
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
     </row>
-    <row r="362" ht="15.75" customHeight="1">
+    <row r="362" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -3458,7 +3572,7 @@
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
     </row>
-    <row r="363" ht="15.75" customHeight="1">
+    <row r="363" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -3466,7 +3580,7 @@
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
     </row>
-    <row r="364" ht="15.75" customHeight="1">
+    <row r="364" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -3474,7 +3588,7 @@
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
     </row>
-    <row r="365" ht="15.75" customHeight="1">
+    <row r="365" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -3482,7 +3596,7 @@
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
     </row>
-    <row r="366" ht="15.75" customHeight="1">
+    <row r="366" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -3490,7 +3604,7 @@
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
     </row>
-    <row r="367" ht="15.75" customHeight="1">
+    <row r="367" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -3498,7 +3612,7 @@
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
     </row>
-    <row r="368" ht="15.75" customHeight="1">
+    <row r="368" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -3506,7 +3620,7 @@
       <c r="E368" s="3"/>
       <c r="F368" s="3"/>
     </row>
-    <row r="369" ht="15.75" customHeight="1">
+    <row r="369" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -3514,7 +3628,7 @@
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
     </row>
-    <row r="370" ht="15.75" customHeight="1">
+    <row r="370" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -3522,7 +3636,7 @@
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
     </row>
-    <row r="371" ht="15.75" customHeight="1">
+    <row r="371" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -3530,7 +3644,7 @@
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
     </row>
-    <row r="372" ht="15.75" customHeight="1">
+    <row r="372" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -3538,7 +3652,7 @@
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
     </row>
-    <row r="373" ht="15.75" customHeight="1">
+    <row r="373" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -3546,7 +3660,7 @@
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
     </row>
-    <row r="374" ht="15.75" customHeight="1">
+    <row r="374" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -3554,7 +3668,7 @@
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
     </row>
-    <row r="375" ht="15.75" customHeight="1">
+    <row r="375" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -3562,7 +3676,7 @@
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
     </row>
-    <row r="376" ht="15.75" customHeight="1">
+    <row r="376" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -3570,7 +3684,7 @@
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
     </row>
-    <row r="377" ht="15.75" customHeight="1">
+    <row r="377" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -3578,7 +3692,7 @@
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
     </row>
-    <row r="378" ht="15.75" customHeight="1">
+    <row r="378" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -3586,7 +3700,7 @@
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
     </row>
-    <row r="379" ht="15.75" customHeight="1">
+    <row r="379" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -3594,7 +3708,7 @@
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
     </row>
-    <row r="380" ht="15.75" customHeight="1">
+    <row r="380" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -3602,7 +3716,7 @@
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>
     </row>
-    <row r="381" ht="15.75" customHeight="1">
+    <row r="381" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -3610,7 +3724,7 @@
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
     </row>
-    <row r="382" ht="15.75" customHeight="1">
+    <row r="382" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -3618,7 +3732,7 @@
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
     </row>
-    <row r="383" ht="15.75" customHeight="1">
+    <row r="383" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -3626,7 +3740,7 @@
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
     </row>
-    <row r="384" ht="15.75" customHeight="1">
+    <row r="384" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -3634,7 +3748,7 @@
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
     </row>
-    <row r="385" ht="15.75" customHeight="1">
+    <row r="385" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -3642,7 +3756,7 @@
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
     </row>
-    <row r="386" ht="15.75" customHeight="1">
+    <row r="386" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -3650,7 +3764,7 @@
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
     </row>
-    <row r="387" ht="15.75" customHeight="1">
+    <row r="387" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -3658,7 +3772,7 @@
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
     </row>
-    <row r="388" ht="15.75" customHeight="1">
+    <row r="388" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -3666,7 +3780,7 @@
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
     </row>
-    <row r="389" ht="15.75" customHeight="1">
+    <row r="389" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -3674,7 +3788,7 @@
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
     </row>
-    <row r="390" ht="15.75" customHeight="1">
+    <row r="390" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -3682,7 +3796,7 @@
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
     </row>
-    <row r="391" ht="15.75" customHeight="1">
+    <row r="391" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -3690,7 +3804,7 @@
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
     </row>
-    <row r="392" ht="15.75" customHeight="1">
+    <row r="392" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -3698,7 +3812,7 @@
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
     </row>
-    <row r="393" ht="15.75" customHeight="1">
+    <row r="393" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -3706,7 +3820,7 @@
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
     </row>
-    <row r="394" ht="15.75" customHeight="1">
+    <row r="394" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -3714,7 +3828,7 @@
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
     </row>
-    <row r="395" ht="15.75" customHeight="1">
+    <row r="395" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -3722,7 +3836,7 @@
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
     </row>
-    <row r="396" ht="15.75" customHeight="1">
+    <row r="396" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -3730,7 +3844,7 @@
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
     </row>
-    <row r="397" ht="15.75" customHeight="1">
+    <row r="397" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -3738,7 +3852,7 @@
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
     </row>
-    <row r="398" ht="15.75" customHeight="1">
+    <row r="398" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -3746,7 +3860,7 @@
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
     </row>
-    <row r="399" ht="15.75" customHeight="1">
+    <row r="399" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -3754,7 +3868,7 @@
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
     </row>
-    <row r="400" ht="15.75" customHeight="1">
+    <row r="400" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -3762,7 +3876,7 @@
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
     </row>
-    <row r="401" ht="15.75" customHeight="1">
+    <row r="401" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -3770,7 +3884,7 @@
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
     </row>
-    <row r="402" ht="15.75" customHeight="1">
+    <row r="402" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -3778,7 +3892,7 @@
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
     </row>
-    <row r="403" ht="15.75" customHeight="1">
+    <row r="403" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -3786,7 +3900,7 @@
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
     </row>
-    <row r="404" ht="15.75" customHeight="1">
+    <row r="404" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -3794,7 +3908,7 @@
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
     </row>
-    <row r="405" ht="15.75" customHeight="1">
+    <row r="405" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -3802,7 +3916,7 @@
       <c r="E405" s="3"/>
       <c r="F405" s="3"/>
     </row>
-    <row r="406" ht="15.75" customHeight="1">
+    <row r="406" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -3810,7 +3924,7 @@
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
     </row>
-    <row r="407" ht="15.75" customHeight="1">
+    <row r="407" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -3818,7 +3932,7 @@
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
     </row>
-    <row r="408" ht="15.75" customHeight="1">
+    <row r="408" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -3826,7 +3940,7 @@
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
     </row>
-    <row r="409" ht="15.75" customHeight="1">
+    <row r="409" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -3834,7 +3948,7 @@
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
     </row>
-    <row r="410" ht="15.75" customHeight="1">
+    <row r="410" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -3842,7 +3956,7 @@
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
     </row>
-    <row r="411" ht="15.75" customHeight="1">
+    <row r="411" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -3850,7 +3964,7 @@
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
     </row>
-    <row r="412" ht="15.75" customHeight="1">
+    <row r="412" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -3858,7 +3972,7 @@
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
     </row>
-    <row r="413" ht="15.75" customHeight="1">
+    <row r="413" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -3866,7 +3980,7 @@
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
     </row>
-    <row r="414" ht="15.75" customHeight="1">
+    <row r="414" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -3874,7 +3988,7 @@
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
     </row>
-    <row r="415" ht="15.75" customHeight="1">
+    <row r="415" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -3882,7 +3996,7 @@
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
     </row>
-    <row r="416" ht="15.75" customHeight="1">
+    <row r="416" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -3890,7 +4004,7 @@
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
     </row>
-    <row r="417" ht="15.75" customHeight="1">
+    <row r="417" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -3898,7 +4012,7 @@
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
     </row>
-    <row r="418" ht="15.75" customHeight="1">
+    <row r="418" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -3906,7 +4020,7 @@
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
     </row>
-    <row r="419" ht="15.75" customHeight="1">
+    <row r="419" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -3914,7 +4028,7 @@
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
     </row>
-    <row r="420" ht="15.75" customHeight="1">
+    <row r="420" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -3922,7 +4036,7 @@
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
     </row>
-    <row r="421" ht="15.75" customHeight="1">
+    <row r="421" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -3930,7 +4044,7 @@
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
     </row>
-    <row r="422" ht="15.75" customHeight="1">
+    <row r="422" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -3938,7 +4052,7 @@
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
     </row>
-    <row r="423" ht="15.75" customHeight="1">
+    <row r="423" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -3946,7 +4060,7 @@
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
     </row>
-    <row r="424" ht="15.75" customHeight="1">
+    <row r="424" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -3954,7 +4068,7 @@
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
     </row>
-    <row r="425" ht="15.75" customHeight="1">
+    <row r="425" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -3962,7 +4076,7 @@
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
     </row>
-    <row r="426" ht="15.75" customHeight="1">
+    <row r="426" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -3970,7 +4084,7 @@
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
     </row>
-    <row r="427" ht="15.75" customHeight="1">
+    <row r="427" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -3978,7 +4092,7 @@
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
     </row>
-    <row r="428" ht="15.75" customHeight="1">
+    <row r="428" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -3986,7 +4100,7 @@
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
     </row>
-    <row r="429" ht="15.75" customHeight="1">
+    <row r="429" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -3994,7 +4108,7 @@
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
     </row>
-    <row r="430" ht="15.75" customHeight="1">
+    <row r="430" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -4002,7 +4116,7 @@
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
     </row>
-    <row r="431" ht="15.75" customHeight="1">
+    <row r="431" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -4010,7 +4124,7 @@
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
     </row>
-    <row r="432" ht="15.75" customHeight="1">
+    <row r="432" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -4018,7 +4132,7 @@
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
     </row>
-    <row r="433" ht="15.75" customHeight="1">
+    <row r="433" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -4026,7 +4140,7 @@
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
     </row>
-    <row r="434" ht="15.75" customHeight="1">
+    <row r="434" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -4034,7 +4148,7 @@
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
     </row>
-    <row r="435" ht="15.75" customHeight="1">
+    <row r="435" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -4042,7 +4156,7 @@
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
     </row>
-    <row r="436" ht="15.75" customHeight="1">
+    <row r="436" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -4050,7 +4164,7 @@
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
     </row>
-    <row r="437" ht="15.75" customHeight="1">
+    <row r="437" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -4058,7 +4172,7 @@
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
     </row>
-    <row r="438" ht="15.75" customHeight="1">
+    <row r="438" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -4066,7 +4180,7 @@
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
     </row>
-    <row r="439" ht="15.75" customHeight="1">
+    <row r="439" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -4074,7 +4188,7 @@
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
     </row>
-    <row r="440" ht="15.75" customHeight="1">
+    <row r="440" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -4082,7 +4196,7 @@
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
     </row>
-    <row r="441" ht="15.75" customHeight="1">
+    <row r="441" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -4090,7 +4204,7 @@
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
     </row>
-    <row r="442" ht="15.75" customHeight="1">
+    <row r="442" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -4098,7 +4212,7 @@
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
     </row>
-    <row r="443" ht="15.75" customHeight="1">
+    <row r="443" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -4106,7 +4220,7 @@
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
     </row>
-    <row r="444" ht="15.75" customHeight="1">
+    <row r="444" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -4114,7 +4228,7 @@
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
     </row>
-    <row r="445" ht="15.75" customHeight="1">
+    <row r="445" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -4122,7 +4236,7 @@
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
     </row>
-    <row r="446" ht="15.75" customHeight="1">
+    <row r="446" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -4130,7 +4244,7 @@
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
     </row>
-    <row r="447" ht="15.75" customHeight="1">
+    <row r="447" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -4138,7 +4252,7 @@
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
     </row>
-    <row r="448" ht="15.75" customHeight="1">
+    <row r="448" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -4146,7 +4260,7 @@
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
     </row>
-    <row r="449" ht="15.75" customHeight="1">
+    <row r="449" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -4154,7 +4268,7 @@
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
     </row>
-    <row r="450" ht="15.75" customHeight="1">
+    <row r="450" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -4162,7 +4276,7 @@
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
     </row>
-    <row r="451" ht="15.75" customHeight="1">
+    <row r="451" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -4170,7 +4284,7 @@
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
     </row>
-    <row r="452" ht="15.75" customHeight="1">
+    <row r="452" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -4178,7 +4292,7 @@
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
     </row>
-    <row r="453" ht="15.75" customHeight="1">
+    <row r="453" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -4186,7 +4300,7 @@
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
     </row>
-    <row r="454" ht="15.75" customHeight="1">
+    <row r="454" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -4194,7 +4308,7 @@
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
     </row>
-    <row r="455" ht="15.75" customHeight="1">
+    <row r="455" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -4202,7 +4316,7 @@
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
     </row>
-    <row r="456" ht="15.75" customHeight="1">
+    <row r="456" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -4210,7 +4324,7 @@
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
     </row>
-    <row r="457" ht="15.75" customHeight="1">
+    <row r="457" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -4218,7 +4332,7 @@
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
     </row>
-    <row r="458" ht="15.75" customHeight="1">
+    <row r="458" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -4226,7 +4340,7 @@
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
     </row>
-    <row r="459" ht="15.75" customHeight="1">
+    <row r="459" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -4234,7 +4348,7 @@
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
     </row>
-    <row r="460" ht="15.75" customHeight="1">
+    <row r="460" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -4242,7 +4356,7 @@
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
     </row>
-    <row r="461" ht="15.75" customHeight="1">
+    <row r="461" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -4250,7 +4364,7 @@
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
     </row>
-    <row r="462" ht="15.75" customHeight="1">
+    <row r="462" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -4258,7 +4372,7 @@
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
     </row>
-    <row r="463" ht="15.75" customHeight="1">
+    <row r="463" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -4266,7 +4380,7 @@
       <c r="E463" s="3"/>
       <c r="F463" s="3"/>
     </row>
-    <row r="464" ht="15.75" customHeight="1">
+    <row r="464" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -4274,7 +4388,7 @@
       <c r="E464" s="3"/>
       <c r="F464" s="3"/>
     </row>
-    <row r="465" ht="15.75" customHeight="1">
+    <row r="465" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -4282,7 +4396,7 @@
       <c r="E465" s="3"/>
       <c r="F465" s="3"/>
     </row>
-    <row r="466" ht="15.75" customHeight="1">
+    <row r="466" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -4290,7 +4404,7 @@
       <c r="E466" s="3"/>
       <c r="F466" s="3"/>
     </row>
-    <row r="467" ht="15.75" customHeight="1">
+    <row r="467" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -4298,7 +4412,7 @@
       <c r="E467" s="3"/>
       <c r="F467" s="3"/>
     </row>
-    <row r="468" ht="15.75" customHeight="1">
+    <row r="468" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -4306,7 +4420,7 @@
       <c r="E468" s="3"/>
       <c r="F468" s="3"/>
     </row>
-    <row r="469" ht="15.75" customHeight="1">
+    <row r="469" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -4314,7 +4428,7 @@
       <c r="E469" s="3"/>
       <c r="F469" s="3"/>
     </row>
-    <row r="470" ht="15.75" customHeight="1">
+    <row r="470" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -4322,7 +4436,7 @@
       <c r="E470" s="3"/>
       <c r="F470" s="3"/>
     </row>
-    <row r="471" ht="15.75" customHeight="1">
+    <row r="471" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -4330,7 +4444,7 @@
       <c r="E471" s="3"/>
       <c r="F471" s="3"/>
     </row>
-    <row r="472" ht="15.75" customHeight="1">
+    <row r="472" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -4338,7 +4452,7 @@
       <c r="E472" s="3"/>
       <c r="F472" s="3"/>
     </row>
-    <row r="473" ht="15.75" customHeight="1">
+    <row r="473" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -4346,7 +4460,7 @@
       <c r="E473" s="3"/>
       <c r="F473" s="3"/>
     </row>
-    <row r="474" ht="15.75" customHeight="1">
+    <row r="474" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -4354,7 +4468,7 @@
       <c r="E474" s="3"/>
       <c r="F474" s="3"/>
     </row>
-    <row r="475" ht="15.75" customHeight="1">
+    <row r="475" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -4362,7 +4476,7 @@
       <c r="E475" s="3"/>
       <c r="F475" s="3"/>
     </row>
-    <row r="476" ht="15.75" customHeight="1">
+    <row r="476" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -4370,7 +4484,7 @@
       <c r="E476" s="3"/>
       <c r="F476" s="3"/>
     </row>
-    <row r="477" ht="15.75" customHeight="1">
+    <row r="477" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -4378,7 +4492,7 @@
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
     </row>
-    <row r="478" ht="15.75" customHeight="1">
+    <row r="478" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -4386,7 +4500,7 @@
       <c r="E478" s="3"/>
       <c r="F478" s="3"/>
     </row>
-    <row r="479" ht="15.75" customHeight="1">
+    <row r="479" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -4394,7 +4508,7 @@
       <c r="E479" s="3"/>
       <c r="F479" s="3"/>
     </row>
-    <row r="480" ht="15.75" customHeight="1">
+    <row r="480" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -4402,7 +4516,7 @@
       <c r="E480" s="3"/>
       <c r="F480" s="3"/>
     </row>
-    <row r="481" ht="15.75" customHeight="1">
+    <row r="481" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -4410,7 +4524,7 @@
       <c r="E481" s="3"/>
       <c r="F481" s="3"/>
     </row>
-    <row r="482" ht="15.75" customHeight="1">
+    <row r="482" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -4418,7 +4532,7 @@
       <c r="E482" s="3"/>
       <c r="F482" s="3"/>
     </row>
-    <row r="483" ht="15.75" customHeight="1">
+    <row r="483" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -4426,7 +4540,7 @@
       <c r="E483" s="3"/>
       <c r="F483" s="3"/>
     </row>
-    <row r="484" ht="15.75" customHeight="1">
+    <row r="484" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -4434,7 +4548,7 @@
       <c r="E484" s="3"/>
       <c r="F484" s="3"/>
     </row>
-    <row r="485" ht="15.75" customHeight="1">
+    <row r="485" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -4442,7 +4556,7 @@
       <c r="E485" s="3"/>
       <c r="F485" s="3"/>
     </row>
-    <row r="486" ht="15.75" customHeight="1">
+    <row r="486" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -4450,7 +4564,7 @@
       <c r="E486" s="3"/>
       <c r="F486" s="3"/>
     </row>
-    <row r="487" ht="15.75" customHeight="1">
+    <row r="487" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -4458,7 +4572,7 @@
       <c r="E487" s="3"/>
       <c r="F487" s="3"/>
     </row>
-    <row r="488" ht="15.75" customHeight="1">
+    <row r="488" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -4466,7 +4580,7 @@
       <c r="E488" s="3"/>
       <c r="F488" s="3"/>
     </row>
-    <row r="489" ht="15.75" customHeight="1">
+    <row r="489" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -4474,7 +4588,7 @@
       <c r="E489" s="3"/>
       <c r="F489" s="3"/>
     </row>
-    <row r="490" ht="15.75" customHeight="1">
+    <row r="490" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -4482,7 +4596,7 @@
       <c r="E490" s="3"/>
       <c r="F490" s="3"/>
     </row>
-    <row r="491" ht="15.75" customHeight="1">
+    <row r="491" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -4490,7 +4604,7 @@
       <c r="E491" s="3"/>
       <c r="F491" s="3"/>
     </row>
-    <row r="492" ht="15.75" customHeight="1">
+    <row r="492" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -4498,7 +4612,7 @@
       <c r="E492" s="3"/>
       <c r="F492" s="3"/>
     </row>
-    <row r="493" ht="15.75" customHeight="1">
+    <row r="493" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -4506,7 +4620,7 @@
       <c r="E493" s="3"/>
       <c r="F493" s="3"/>
     </row>
-    <row r="494" ht="15.75" customHeight="1">
+    <row r="494" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -4514,7 +4628,7 @@
       <c r="E494" s="3"/>
       <c r="F494" s="3"/>
     </row>
-    <row r="495" ht="15.75" customHeight="1">
+    <row r="495" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -4522,7 +4636,7 @@
       <c r="E495" s="3"/>
       <c r="F495" s="3"/>
     </row>
-    <row r="496" ht="15.75" customHeight="1">
+    <row r="496" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -4530,7 +4644,7 @@
       <c r="E496" s="3"/>
       <c r="F496" s="3"/>
     </row>
-    <row r="497" ht="15.75" customHeight="1">
+    <row r="497" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -4538,7 +4652,7 @@
       <c r="E497" s="3"/>
       <c r="F497" s="3"/>
     </row>
-    <row r="498" ht="15.75" customHeight="1">
+    <row r="498" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -4546,7 +4660,7 @@
       <c r="E498" s="3"/>
       <c r="F498" s="3"/>
     </row>
-    <row r="499" ht="15.75" customHeight="1">
+    <row r="499" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -4554,7 +4668,7 @@
       <c r="E499" s="3"/>
       <c r="F499" s="3"/>
     </row>
-    <row r="500" ht="15.75" customHeight="1">
+    <row r="500" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -4562,7 +4676,7 @@
       <c r="E500" s="3"/>
       <c r="F500" s="3"/>
     </row>
-    <row r="501" ht="15.75" customHeight="1">
+    <row r="501" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -4570,7 +4684,7 @@
       <c r="E501" s="3"/>
       <c r="F501" s="3"/>
     </row>
-    <row r="502" ht="15.75" customHeight="1">
+    <row r="502" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -4578,7 +4692,7 @@
       <c r="E502" s="3"/>
       <c r="F502" s="3"/>
     </row>
-    <row r="503" ht="15.75" customHeight="1">
+    <row r="503" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -4586,7 +4700,7 @@
       <c r="E503" s="3"/>
       <c r="F503" s="3"/>
     </row>
-    <row r="504" ht="15.75" customHeight="1">
+    <row r="504" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -4594,7 +4708,7 @@
       <c r="E504" s="3"/>
       <c r="F504" s="3"/>
     </row>
-    <row r="505" ht="15.75" customHeight="1">
+    <row r="505" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -4602,7 +4716,7 @@
       <c r="E505" s="3"/>
       <c r="F505" s="3"/>
     </row>
-    <row r="506" ht="15.75" customHeight="1">
+    <row r="506" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -4610,7 +4724,7 @@
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
     </row>
-    <row r="507" ht="15.75" customHeight="1">
+    <row r="507" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -4618,7 +4732,7 @@
       <c r="E507" s="3"/>
       <c r="F507" s="3"/>
     </row>
-    <row r="508" ht="15.75" customHeight="1">
+    <row r="508" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -4626,7 +4740,7 @@
       <c r="E508" s="3"/>
       <c r="F508" s="3"/>
     </row>
-    <row r="509" ht="15.75" customHeight="1">
+    <row r="509" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -4634,7 +4748,7 @@
       <c r="E509" s="3"/>
       <c r="F509" s="3"/>
     </row>
-    <row r="510" ht="15.75" customHeight="1">
+    <row r="510" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -4642,7 +4756,7 @@
       <c r="E510" s="3"/>
       <c r="F510" s="3"/>
     </row>
-    <row r="511" ht="15.75" customHeight="1">
+    <row r="511" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -4650,7 +4764,7 @@
       <c r="E511" s="3"/>
       <c r="F511" s="3"/>
     </row>
-    <row r="512" ht="15.75" customHeight="1">
+    <row r="512" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -4658,7 +4772,7 @@
       <c r="E512" s="3"/>
       <c r="F512" s="3"/>
     </row>
-    <row r="513" ht="15.75" customHeight="1">
+    <row r="513" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -4666,7 +4780,7 @@
       <c r="E513" s="3"/>
       <c r="F513" s="3"/>
     </row>
-    <row r="514" ht="15.75" customHeight="1">
+    <row r="514" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -4674,7 +4788,7 @@
       <c r="E514" s="3"/>
       <c r="F514" s="3"/>
     </row>
-    <row r="515" ht="15.75" customHeight="1">
+    <row r="515" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -4682,7 +4796,7 @@
       <c r="E515" s="3"/>
       <c r="F515" s="3"/>
     </row>
-    <row r="516" ht="15.75" customHeight="1">
+    <row r="516" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -4690,7 +4804,7 @@
       <c r="E516" s="3"/>
       <c r="F516" s="3"/>
     </row>
-    <row r="517" ht="15.75" customHeight="1">
+    <row r="517" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -4698,7 +4812,7 @@
       <c r="E517" s="3"/>
       <c r="F517" s="3"/>
     </row>
-    <row r="518" ht="15.75" customHeight="1">
+    <row r="518" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -4706,7 +4820,7 @@
       <c r="E518" s="3"/>
       <c r="F518" s="3"/>
     </row>
-    <row r="519" ht="15.75" customHeight="1">
+    <row r="519" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -4714,7 +4828,7 @@
       <c r="E519" s="3"/>
       <c r="F519" s="3"/>
     </row>
-    <row r="520" ht="15.75" customHeight="1">
+    <row r="520" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -4722,7 +4836,7 @@
       <c r="E520" s="3"/>
       <c r="F520" s="3"/>
     </row>
-    <row r="521" ht="15.75" customHeight="1">
+    <row r="521" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -4730,7 +4844,7 @@
       <c r="E521" s="3"/>
       <c r="F521" s="3"/>
     </row>
-    <row r="522" ht="15.75" customHeight="1">
+    <row r="522" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -4738,7 +4852,7 @@
       <c r="E522" s="3"/>
       <c r="F522" s="3"/>
     </row>
-    <row r="523" ht="15.75" customHeight="1">
+    <row r="523" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -4746,7 +4860,7 @@
       <c r="E523" s="3"/>
       <c r="F523" s="3"/>
     </row>
-    <row r="524" ht="15.75" customHeight="1">
+    <row r="524" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -4754,7 +4868,7 @@
       <c r="E524" s="3"/>
       <c r="F524" s="3"/>
     </row>
-    <row r="525" ht="15.75" customHeight="1">
+    <row r="525" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -4762,7 +4876,7 @@
       <c r="E525" s="3"/>
       <c r="F525" s="3"/>
     </row>
-    <row r="526" ht="15.75" customHeight="1">
+    <row r="526" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -4770,7 +4884,7 @@
       <c r="E526" s="3"/>
       <c r="F526" s="3"/>
     </row>
-    <row r="527" ht="15.75" customHeight="1">
+    <row r="527" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -4778,7 +4892,7 @@
       <c r="E527" s="3"/>
       <c r="F527" s="3"/>
     </row>
-    <row r="528" ht="15.75" customHeight="1">
+    <row r="528" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -4786,7 +4900,7 @@
       <c r="E528" s="3"/>
       <c r="F528" s="3"/>
     </row>
-    <row r="529" ht="15.75" customHeight="1">
+    <row r="529" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -4794,7 +4908,7 @@
       <c r="E529" s="3"/>
       <c r="F529" s="3"/>
     </row>
-    <row r="530" ht="15.75" customHeight="1">
+    <row r="530" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -4802,7 +4916,7 @@
       <c r="E530" s="3"/>
       <c r="F530" s="3"/>
     </row>
-    <row r="531" ht="15.75" customHeight="1">
+    <row r="531" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -4810,7 +4924,7 @@
       <c r="E531" s="3"/>
       <c r="F531" s="3"/>
     </row>
-    <row r="532" ht="15.75" customHeight="1">
+    <row r="532" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -4818,7 +4932,7 @@
       <c r="E532" s="3"/>
       <c r="F532" s="3"/>
     </row>
-    <row r="533" ht="15.75" customHeight="1">
+    <row r="533" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -4826,7 +4940,7 @@
       <c r="E533" s="3"/>
       <c r="F533" s="3"/>
     </row>
-    <row r="534" ht="15.75" customHeight="1">
+    <row r="534" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -4834,7 +4948,7 @@
       <c r="E534" s="3"/>
       <c r="F534" s="3"/>
     </row>
-    <row r="535" ht="15.75" customHeight="1">
+    <row r="535" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -4842,7 +4956,7 @@
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
     </row>
-    <row r="536" ht="15.75" customHeight="1">
+    <row r="536" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -4850,7 +4964,7 @@
       <c r="E536" s="3"/>
       <c r="F536" s="3"/>
     </row>
-    <row r="537" ht="15.75" customHeight="1">
+    <row r="537" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -4858,7 +4972,7 @@
       <c r="E537" s="3"/>
       <c r="F537" s="3"/>
     </row>
-    <row r="538" ht="15.75" customHeight="1">
+    <row r="538" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -4866,7 +4980,7 @@
       <c r="E538" s="3"/>
       <c r="F538" s="3"/>
     </row>
-    <row r="539" ht="15.75" customHeight="1">
+    <row r="539" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -4874,7 +4988,7 @@
       <c r="E539" s="3"/>
       <c r="F539" s="3"/>
     </row>
-    <row r="540" ht="15.75" customHeight="1">
+    <row r="540" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -4882,7 +4996,7 @@
       <c r="E540" s="3"/>
       <c r="F540" s="3"/>
     </row>
-    <row r="541" ht="15.75" customHeight="1">
+    <row r="541" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -4890,7 +5004,7 @@
       <c r="E541" s="3"/>
       <c r="F541" s="3"/>
     </row>
-    <row r="542" ht="15.75" customHeight="1">
+    <row r="542" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -4898,7 +5012,7 @@
       <c r="E542" s="3"/>
       <c r="F542" s="3"/>
     </row>
-    <row r="543" ht="15.75" customHeight="1">
+    <row r="543" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -4906,7 +5020,7 @@
       <c r="E543" s="3"/>
       <c r="F543" s="3"/>
     </row>
-    <row r="544" ht="15.75" customHeight="1">
+    <row r="544" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -4914,7 +5028,7 @@
       <c r="E544" s="3"/>
       <c r="F544" s="3"/>
     </row>
-    <row r="545" ht="15.75" customHeight="1">
+    <row r="545" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -4922,7 +5036,7 @@
       <c r="E545" s="3"/>
       <c r="F545" s="3"/>
     </row>
-    <row r="546" ht="15.75" customHeight="1">
+    <row r="546" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -4930,7 +5044,7 @@
       <c r="E546" s="3"/>
       <c r="F546" s="3"/>
     </row>
-    <row r="547" ht="15.75" customHeight="1">
+    <row r="547" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -4938,7 +5052,7 @@
       <c r="E547" s="3"/>
       <c r="F547" s="3"/>
     </row>
-    <row r="548" ht="15.75" customHeight="1">
+    <row r="548" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -4946,7 +5060,7 @@
       <c r="E548" s="3"/>
       <c r="F548" s="3"/>
     </row>
-    <row r="549" ht="15.75" customHeight="1">
+    <row r="549" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -4954,7 +5068,7 @@
       <c r="E549" s="3"/>
       <c r="F549" s="3"/>
     </row>
-    <row r="550" ht="15.75" customHeight="1">
+    <row r="550" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -4962,7 +5076,7 @@
       <c r="E550" s="3"/>
       <c r="F550" s="3"/>
     </row>
-    <row r="551" ht="15.75" customHeight="1">
+    <row r="551" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -4970,7 +5084,7 @@
       <c r="E551" s="3"/>
       <c r="F551" s="3"/>
     </row>
-    <row r="552" ht="15.75" customHeight="1">
+    <row r="552" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -4978,7 +5092,7 @@
       <c r="E552" s="3"/>
       <c r="F552" s="3"/>
     </row>
-    <row r="553" ht="15.75" customHeight="1">
+    <row r="553" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -4986,7 +5100,7 @@
       <c r="E553" s="3"/>
       <c r="F553" s="3"/>
     </row>
-    <row r="554" ht="15.75" customHeight="1">
+    <row r="554" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -4994,7 +5108,7 @@
       <c r="E554" s="3"/>
       <c r="F554" s="3"/>
     </row>
-    <row r="555" ht="15.75" customHeight="1">
+    <row r="555" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -5002,7 +5116,7 @@
       <c r="E555" s="3"/>
       <c r="F555" s="3"/>
     </row>
-    <row r="556" ht="15.75" customHeight="1">
+    <row r="556" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -5010,7 +5124,7 @@
       <c r="E556" s="3"/>
       <c r="F556" s="3"/>
     </row>
-    <row r="557" ht="15.75" customHeight="1">
+    <row r="557" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -5018,7 +5132,7 @@
       <c r="E557" s="3"/>
       <c r="F557" s="3"/>
     </row>
-    <row r="558" ht="15.75" customHeight="1">
+    <row r="558" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -5026,7 +5140,7 @@
       <c r="E558" s="3"/>
       <c r="F558" s="3"/>
     </row>
-    <row r="559" ht="15.75" customHeight="1">
+    <row r="559" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -5034,7 +5148,7 @@
       <c r="E559" s="3"/>
       <c r="F559" s="3"/>
     </row>
-    <row r="560" ht="15.75" customHeight="1">
+    <row r="560" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -5042,7 +5156,7 @@
       <c r="E560" s="3"/>
       <c r="F560" s="3"/>
     </row>
-    <row r="561" ht="15.75" customHeight="1">
+    <row r="561" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -5050,7 +5164,7 @@
       <c r="E561" s="3"/>
       <c r="F561" s="3"/>
     </row>
-    <row r="562" ht="15.75" customHeight="1">
+    <row r="562" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -5058,7 +5172,7 @@
       <c r="E562" s="3"/>
       <c r="F562" s="3"/>
     </row>
-    <row r="563" ht="15.75" customHeight="1">
+    <row r="563" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -5066,7 +5180,7 @@
       <c r="E563" s="3"/>
       <c r="F563" s="3"/>
     </row>
-    <row r="564" ht="15.75" customHeight="1">
+    <row r="564" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -5074,7 +5188,7 @@
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
     </row>
-    <row r="565" ht="15.75" customHeight="1">
+    <row r="565" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -5082,7 +5196,7 @@
       <c r="E565" s="3"/>
       <c r="F565" s="3"/>
     </row>
-    <row r="566" ht="15.75" customHeight="1">
+    <row r="566" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -5090,7 +5204,7 @@
       <c r="E566" s="3"/>
       <c r="F566" s="3"/>
     </row>
-    <row r="567" ht="15.75" customHeight="1">
+    <row r="567" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -5098,7 +5212,7 @@
       <c r="E567" s="3"/>
       <c r="F567" s="3"/>
     </row>
-    <row r="568" ht="15.75" customHeight="1">
+    <row r="568" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -5106,7 +5220,7 @@
       <c r="E568" s="3"/>
       <c r="F568" s="3"/>
     </row>
-    <row r="569" ht="15.75" customHeight="1">
+    <row r="569" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -5114,7 +5228,7 @@
       <c r="E569" s="3"/>
       <c r="F569" s="3"/>
     </row>
-    <row r="570" ht="15.75" customHeight="1">
+    <row r="570" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -5122,7 +5236,7 @@
       <c r="E570" s="3"/>
       <c r="F570" s="3"/>
     </row>
-    <row r="571" ht="15.75" customHeight="1">
+    <row r="571" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -5130,7 +5244,7 @@
       <c r="E571" s="3"/>
       <c r="F571" s="3"/>
     </row>
-    <row r="572" ht="15.75" customHeight="1">
+    <row r="572" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -5138,7 +5252,7 @@
       <c r="E572" s="3"/>
       <c r="F572" s="3"/>
     </row>
-    <row r="573" ht="15.75" customHeight="1">
+    <row r="573" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -5146,7 +5260,7 @@
       <c r="E573" s="3"/>
       <c r="F573" s="3"/>
     </row>
-    <row r="574" ht="15.75" customHeight="1">
+    <row r="574" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -5154,7 +5268,7 @@
       <c r="E574" s="3"/>
       <c r="F574" s="3"/>
     </row>
-    <row r="575" ht="15.75" customHeight="1">
+    <row r="575" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -5162,7 +5276,7 @@
       <c r="E575" s="3"/>
       <c r="F575" s="3"/>
     </row>
-    <row r="576" ht="15.75" customHeight="1">
+    <row r="576" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -5170,7 +5284,7 @@
       <c r="E576" s="3"/>
       <c r="F576" s="3"/>
     </row>
-    <row r="577" ht="15.75" customHeight="1">
+    <row r="577" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -5178,7 +5292,7 @@
       <c r="E577" s="3"/>
       <c r="F577" s="3"/>
     </row>
-    <row r="578" ht="15.75" customHeight="1">
+    <row r="578" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -5186,7 +5300,7 @@
       <c r="E578" s="3"/>
       <c r="F578" s="3"/>
     </row>
-    <row r="579" ht="15.75" customHeight="1">
+    <row r="579" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -5194,7 +5308,7 @@
       <c r="E579" s="3"/>
       <c r="F579" s="3"/>
     </row>
-    <row r="580" ht="15.75" customHeight="1">
+    <row r="580" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -5202,7 +5316,7 @@
       <c r="E580" s="3"/>
       <c r="F580" s="3"/>
     </row>
-    <row r="581" ht="15.75" customHeight="1">
+    <row r="581" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -5210,7 +5324,7 @@
       <c r="E581" s="3"/>
       <c r="F581" s="3"/>
     </row>
-    <row r="582" ht="15.75" customHeight="1">
+    <row r="582" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -5218,7 +5332,7 @@
       <c r="E582" s="3"/>
       <c r="F582" s="3"/>
     </row>
-    <row r="583" ht="15.75" customHeight="1">
+    <row r="583" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -5226,7 +5340,7 @@
       <c r="E583" s="3"/>
       <c r="F583" s="3"/>
     </row>
-    <row r="584" ht="15.75" customHeight="1">
+    <row r="584" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -5234,7 +5348,7 @@
       <c r="E584" s="3"/>
       <c r="F584" s="3"/>
     </row>
-    <row r="585" ht="15.75" customHeight="1">
+    <row r="585" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -5242,7 +5356,7 @@
       <c r="E585" s="3"/>
       <c r="F585" s="3"/>
     </row>
-    <row r="586" ht="15.75" customHeight="1">
+    <row r="586" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -5250,7 +5364,7 @@
       <c r="E586" s="3"/>
       <c r="F586" s="3"/>
     </row>
-    <row r="587" ht="15.75" customHeight="1">
+    <row r="587" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -5258,7 +5372,7 @@
       <c r="E587" s="3"/>
       <c r="F587" s="3"/>
     </row>
-    <row r="588" ht="15.75" customHeight="1">
+    <row r="588" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -5266,7 +5380,7 @@
       <c r="E588" s="3"/>
       <c r="F588" s="3"/>
     </row>
-    <row r="589" ht="15.75" customHeight="1">
+    <row r="589" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -5274,7 +5388,7 @@
       <c r="E589" s="3"/>
       <c r="F589" s="3"/>
     </row>
-    <row r="590" ht="15.75" customHeight="1">
+    <row r="590" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -5282,7 +5396,7 @@
       <c r="E590" s="3"/>
       <c r="F590" s="3"/>
     </row>
-    <row r="591" ht="15.75" customHeight="1">
+    <row r="591" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -5290,7 +5404,7 @@
       <c r="E591" s="3"/>
       <c r="F591" s="3"/>
     </row>
-    <row r="592" ht="15.75" customHeight="1">
+    <row r="592" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -5298,7 +5412,7 @@
       <c r="E592" s="3"/>
       <c r="F592" s="3"/>
     </row>
-    <row r="593" ht="15.75" customHeight="1">
+    <row r="593" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -5306,7 +5420,7 @@
       <c r="E593" s="3"/>
       <c r="F593" s="3"/>
     </row>
-    <row r="594" ht="15.75" customHeight="1">
+    <row r="594" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -5314,7 +5428,7 @@
       <c r="E594" s="3"/>
       <c r="F594" s="3"/>
     </row>
-    <row r="595" ht="15.75" customHeight="1">
+    <row r="595" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -5322,7 +5436,7 @@
       <c r="E595" s="3"/>
       <c r="F595" s="3"/>
     </row>
-    <row r="596" ht="15.75" customHeight="1">
+    <row r="596" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -5330,7 +5444,7 @@
       <c r="E596" s="3"/>
       <c r="F596" s="3"/>
     </row>
-    <row r="597" ht="15.75" customHeight="1">
+    <row r="597" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -5338,7 +5452,7 @@
       <c r="E597" s="3"/>
       <c r="F597" s="3"/>
     </row>
-    <row r="598" ht="15.75" customHeight="1">
+    <row r="598" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -5346,7 +5460,7 @@
       <c r="E598" s="3"/>
       <c r="F598" s="3"/>
     </row>
-    <row r="599" ht="15.75" customHeight="1">
+    <row r="599" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -5354,7 +5468,7 @@
       <c r="E599" s="3"/>
       <c r="F599" s="3"/>
     </row>
-    <row r="600" ht="15.75" customHeight="1">
+    <row r="600" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -5362,7 +5476,7 @@
       <c r="E600" s="3"/>
       <c r="F600" s="3"/>
     </row>
-    <row r="601" ht="15.75" customHeight="1">
+    <row r="601" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -5370,7 +5484,7 @@
       <c r="E601" s="3"/>
       <c r="F601" s="3"/>
     </row>
-    <row r="602" ht="15.75" customHeight="1">
+    <row r="602" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -5378,7 +5492,7 @@
       <c r="E602" s="3"/>
       <c r="F602" s="3"/>
     </row>
-    <row r="603" ht="15.75" customHeight="1">
+    <row r="603" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -5386,7 +5500,7 @@
       <c r="E603" s="3"/>
       <c r="F603" s="3"/>
     </row>
-    <row r="604" ht="15.75" customHeight="1">
+    <row r="604" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -5394,7 +5508,7 @@
       <c r="E604" s="3"/>
       <c r="F604" s="3"/>
     </row>
-    <row r="605" ht="15.75" customHeight="1">
+    <row r="605" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -5402,7 +5516,7 @@
       <c r="E605" s="3"/>
       <c r="F605" s="3"/>
     </row>
-    <row r="606" ht="15.75" customHeight="1">
+    <row r="606" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -5410,7 +5524,7 @@
       <c r="E606" s="3"/>
       <c r="F606" s="3"/>
     </row>
-    <row r="607" ht="15.75" customHeight="1">
+    <row r="607" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -5418,7 +5532,7 @@
       <c r="E607" s="3"/>
       <c r="F607" s="3"/>
     </row>
-    <row r="608" ht="15.75" customHeight="1">
+    <row r="608" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -5426,7 +5540,7 @@
       <c r="E608" s="3"/>
       <c r="F608" s="3"/>
     </row>
-    <row r="609" ht="15.75" customHeight="1">
+    <row r="609" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -5434,7 +5548,7 @@
       <c r="E609" s="3"/>
       <c r="F609" s="3"/>
     </row>
-    <row r="610" ht="15.75" customHeight="1">
+    <row r="610" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -5442,7 +5556,7 @@
       <c r="E610" s="3"/>
       <c r="F610" s="3"/>
     </row>
-    <row r="611" ht="15.75" customHeight="1">
+    <row r="611" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -5450,7 +5564,7 @@
       <c r="E611" s="3"/>
       <c r="F611" s="3"/>
     </row>
-    <row r="612" ht="15.75" customHeight="1">
+    <row r="612" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -5458,7 +5572,7 @@
       <c r="E612" s="3"/>
       <c r="F612" s="3"/>
     </row>
-    <row r="613" ht="15.75" customHeight="1">
+    <row r="613" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -5466,7 +5580,7 @@
       <c r="E613" s="3"/>
       <c r="F613" s="3"/>
     </row>
-    <row r="614" ht="15.75" customHeight="1">
+    <row r="614" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -5474,7 +5588,7 @@
       <c r="E614" s="3"/>
       <c r="F614" s="3"/>
     </row>
-    <row r="615" ht="15.75" customHeight="1">
+    <row r="615" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -5482,7 +5596,7 @@
       <c r="E615" s="3"/>
       <c r="F615" s="3"/>
     </row>
-    <row r="616" ht="15.75" customHeight="1">
+    <row r="616" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -5490,7 +5604,7 @@
       <c r="E616" s="3"/>
       <c r="F616" s="3"/>
     </row>
-    <row r="617" ht="15.75" customHeight="1">
+    <row r="617" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -5498,7 +5612,7 @@
       <c r="E617" s="3"/>
       <c r="F617" s="3"/>
     </row>
-    <row r="618" ht="15.75" customHeight="1">
+    <row r="618" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -5506,7 +5620,7 @@
       <c r="E618" s="3"/>
       <c r="F618" s="3"/>
     </row>
-    <row r="619" ht="15.75" customHeight="1">
+    <row r="619" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -5514,7 +5628,7 @@
       <c r="E619" s="3"/>
       <c r="F619" s="3"/>
     </row>
-    <row r="620" ht="15.75" customHeight="1">
+    <row r="620" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -5522,7 +5636,7 @@
       <c r="E620" s="3"/>
       <c r="F620" s="3"/>
     </row>
-    <row r="621" ht="15.75" customHeight="1">
+    <row r="621" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -5530,7 +5644,7 @@
       <c r="E621" s="3"/>
       <c r="F621" s="3"/>
     </row>
-    <row r="622" ht="15.75" customHeight="1">
+    <row r="622" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -5538,7 +5652,7 @@
       <c r="E622" s="3"/>
       <c r="F622" s="3"/>
     </row>
-    <row r="623" ht="15.75" customHeight="1">
+    <row r="623" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -5546,7 +5660,7 @@
       <c r="E623" s="3"/>
       <c r="F623" s="3"/>
     </row>
-    <row r="624" ht="15.75" customHeight="1">
+    <row r="624" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -5554,7 +5668,7 @@
       <c r="E624" s="3"/>
       <c r="F624" s="3"/>
     </row>
-    <row r="625" ht="15.75" customHeight="1">
+    <row r="625" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -5562,7 +5676,7 @@
       <c r="E625" s="3"/>
       <c r="F625" s="3"/>
     </row>
-    <row r="626" ht="15.75" customHeight="1">
+    <row r="626" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -5570,7 +5684,7 @@
       <c r="E626" s="3"/>
       <c r="F626" s="3"/>
     </row>
-    <row r="627" ht="15.75" customHeight="1">
+    <row r="627" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -5578,7 +5692,7 @@
       <c r="E627" s="3"/>
       <c r="F627" s="3"/>
     </row>
-    <row r="628" ht="15.75" customHeight="1">
+    <row r="628" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -5586,7 +5700,7 @@
       <c r="E628" s="3"/>
       <c r="F628" s="3"/>
     </row>
-    <row r="629" ht="15.75" customHeight="1">
+    <row r="629" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -5594,7 +5708,7 @@
       <c r="E629" s="3"/>
       <c r="F629" s="3"/>
     </row>
-    <row r="630" ht="15.75" customHeight="1">
+    <row r="630" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -5602,7 +5716,7 @@
       <c r="E630" s="3"/>
       <c r="F630" s="3"/>
     </row>
-    <row r="631" ht="15.75" customHeight="1">
+    <row r="631" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -5610,7 +5724,7 @@
       <c r="E631" s="3"/>
       <c r="F631" s="3"/>
     </row>
-    <row r="632" ht="15.75" customHeight="1">
+    <row r="632" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -5618,7 +5732,7 @@
       <c r="E632" s="3"/>
       <c r="F632" s="3"/>
     </row>
-    <row r="633" ht="15.75" customHeight="1">
+    <row r="633" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -5626,7 +5740,7 @@
       <c r="E633" s="3"/>
       <c r="F633" s="3"/>
     </row>
-    <row r="634" ht="15.75" customHeight="1">
+    <row r="634" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -5634,7 +5748,7 @@
       <c r="E634" s="3"/>
       <c r="F634" s="3"/>
     </row>
-    <row r="635" ht="15.75" customHeight="1">
+    <row r="635" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -5642,7 +5756,7 @@
       <c r="E635" s="3"/>
       <c r="F635" s="3"/>
     </row>
-    <row r="636" ht="15.75" customHeight="1">
+    <row r="636" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -5650,7 +5764,7 @@
       <c r="E636" s="3"/>
       <c r="F636" s="3"/>
     </row>
-    <row r="637" ht="15.75" customHeight="1">
+    <row r="637" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -5658,7 +5772,7 @@
       <c r="E637" s="3"/>
       <c r="F637" s="3"/>
     </row>
-    <row r="638" ht="15.75" customHeight="1">
+    <row r="638" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -5666,7 +5780,7 @@
       <c r="E638" s="3"/>
       <c r="F638" s="3"/>
     </row>
-    <row r="639" ht="15.75" customHeight="1">
+    <row r="639" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -5674,7 +5788,7 @@
       <c r="E639" s="3"/>
       <c r="F639" s="3"/>
     </row>
-    <row r="640" ht="15.75" customHeight="1">
+    <row r="640" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -5682,7 +5796,7 @@
       <c r="E640" s="3"/>
       <c r="F640" s="3"/>
     </row>
-    <row r="641" ht="15.75" customHeight="1">
+    <row r="641" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -5690,7 +5804,7 @@
       <c r="E641" s="3"/>
       <c r="F641" s="3"/>
     </row>
-    <row r="642" ht="15.75" customHeight="1">
+    <row r="642" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -5698,7 +5812,7 @@
       <c r="E642" s="3"/>
       <c r="F642" s="3"/>
     </row>
-    <row r="643" ht="15.75" customHeight="1">
+    <row r="643" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -5706,7 +5820,7 @@
       <c r="E643" s="3"/>
       <c r="F643" s="3"/>
     </row>
-    <row r="644" ht="15.75" customHeight="1">
+    <row r="644" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -5714,7 +5828,7 @@
       <c r="E644" s="3"/>
       <c r="F644" s="3"/>
     </row>
-    <row r="645" ht="15.75" customHeight="1">
+    <row r="645" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -5722,7 +5836,7 @@
       <c r="E645" s="3"/>
       <c r="F645" s="3"/>
     </row>
-    <row r="646" ht="15.75" customHeight="1">
+    <row r="646" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -5730,7 +5844,7 @@
       <c r="E646" s="3"/>
       <c r="F646" s="3"/>
     </row>
-    <row r="647" ht="15.75" customHeight="1">
+    <row r="647" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -5738,7 +5852,7 @@
       <c r="E647" s="3"/>
       <c r="F647" s="3"/>
     </row>
-    <row r="648" ht="15.75" customHeight="1">
+    <row r="648" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -5746,7 +5860,7 @@
       <c r="E648" s="3"/>
       <c r="F648" s="3"/>
     </row>
-    <row r="649" ht="15.75" customHeight="1">
+    <row r="649" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -5754,7 +5868,7 @@
       <c r="E649" s="3"/>
       <c r="F649" s="3"/>
     </row>
-    <row r="650" ht="15.75" customHeight="1">
+    <row r="650" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -5762,7 +5876,7 @@
       <c r="E650" s="3"/>
       <c r="F650" s="3"/>
     </row>
-    <row r="651" ht="15.75" customHeight="1">
+    <row r="651" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -5770,7 +5884,7 @@
       <c r="E651" s="3"/>
       <c r="F651" s="3"/>
     </row>
-    <row r="652" ht="15.75" customHeight="1">
+    <row r="652" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -5778,7 +5892,7 @@
       <c r="E652" s="3"/>
       <c r="F652" s="3"/>
     </row>
-    <row r="653" ht="15.75" customHeight="1">
+    <row r="653" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -5786,7 +5900,7 @@
       <c r="E653" s="3"/>
       <c r="F653" s="3"/>
     </row>
-    <row r="654" ht="15.75" customHeight="1">
+    <row r="654" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -5794,7 +5908,7 @@
       <c r="E654" s="3"/>
       <c r="F654" s="3"/>
     </row>
-    <row r="655" ht="15.75" customHeight="1">
+    <row r="655" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -5802,7 +5916,7 @@
       <c r="E655" s="3"/>
       <c r="F655" s="3"/>
     </row>
-    <row r="656" ht="15.75" customHeight="1">
+    <row r="656" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -5810,7 +5924,7 @@
       <c r="E656" s="3"/>
       <c r="F656" s="3"/>
     </row>
-    <row r="657" ht="15.75" customHeight="1">
+    <row r="657" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -5818,7 +5932,7 @@
       <c r="E657" s="3"/>
       <c r="F657" s="3"/>
     </row>
-    <row r="658" ht="15.75" customHeight="1">
+    <row r="658" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -5826,7 +5940,7 @@
       <c r="E658" s="3"/>
       <c r="F658" s="3"/>
     </row>
-    <row r="659" ht="15.75" customHeight="1">
+    <row r="659" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -5834,7 +5948,7 @@
       <c r="E659" s="3"/>
       <c r="F659" s="3"/>
     </row>
-    <row r="660" ht="15.75" customHeight="1">
+    <row r="660" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -5842,7 +5956,7 @@
       <c r="E660" s="3"/>
       <c r="F660" s="3"/>
     </row>
-    <row r="661" ht="15.75" customHeight="1">
+    <row r="661" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -5850,7 +5964,7 @@
       <c r="E661" s="3"/>
       <c r="F661" s="3"/>
     </row>
-    <row r="662" ht="15.75" customHeight="1">
+    <row r="662" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -5858,7 +5972,7 @@
       <c r="E662" s="3"/>
       <c r="F662" s="3"/>
     </row>
-    <row r="663" ht="15.75" customHeight="1">
+    <row r="663" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -5866,7 +5980,7 @@
       <c r="E663" s="3"/>
       <c r="F663" s="3"/>
     </row>
-    <row r="664" ht="15.75" customHeight="1">
+    <row r="664" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -5874,7 +5988,7 @@
       <c r="E664" s="3"/>
       <c r="F664" s="3"/>
     </row>
-    <row r="665" ht="15.75" customHeight="1">
+    <row r="665" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -5882,7 +5996,7 @@
       <c r="E665" s="3"/>
       <c r="F665" s="3"/>
     </row>
-    <row r="666" ht="15.75" customHeight="1">
+    <row r="666" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -5890,7 +6004,7 @@
       <c r="E666" s="3"/>
       <c r="F666" s="3"/>
     </row>
-    <row r="667" ht="15.75" customHeight="1">
+    <row r="667" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -5898,7 +6012,7 @@
       <c r="E667" s="3"/>
       <c r="F667" s="3"/>
     </row>
-    <row r="668" ht="15.75" customHeight="1">
+    <row r="668" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -5906,7 +6020,7 @@
       <c r="E668" s="3"/>
       <c r="F668" s="3"/>
     </row>
-    <row r="669" ht="15.75" customHeight="1">
+    <row r="669" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -5914,7 +6028,7 @@
       <c r="E669" s="3"/>
       <c r="F669" s="3"/>
     </row>
-    <row r="670" ht="15.75" customHeight="1">
+    <row r="670" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -5922,7 +6036,7 @@
       <c r="E670" s="3"/>
       <c r="F670" s="3"/>
     </row>
-    <row r="671" ht="15.75" customHeight="1">
+    <row r="671" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -5930,7 +6044,7 @@
       <c r="E671" s="3"/>
       <c r="F671" s="3"/>
     </row>
-    <row r="672" ht="15.75" customHeight="1">
+    <row r="672" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -5938,7 +6052,7 @@
       <c r="E672" s="3"/>
       <c r="F672" s="3"/>
     </row>
-    <row r="673" ht="15.75" customHeight="1">
+    <row r="673" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -5946,7 +6060,7 @@
       <c r="E673" s="3"/>
       <c r="F673" s="3"/>
     </row>
-    <row r="674" ht="15.75" customHeight="1">
+    <row r="674" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -5954,7 +6068,7 @@
       <c r="E674" s="3"/>
       <c r="F674" s="3"/>
     </row>
-    <row r="675" ht="15.75" customHeight="1">
+    <row r="675" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -5962,7 +6076,7 @@
       <c r="E675" s="3"/>
       <c r="F675" s="3"/>
     </row>
-    <row r="676" ht="15.75" customHeight="1">
+    <row r="676" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -5970,7 +6084,7 @@
       <c r="E676" s="3"/>
       <c r="F676" s="3"/>
     </row>
-    <row r="677" ht="15.75" customHeight="1">
+    <row r="677" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -5978,7 +6092,7 @@
       <c r="E677" s="3"/>
       <c r="F677" s="3"/>
     </row>
-    <row r="678" ht="15.75" customHeight="1">
+    <row r="678" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -5986,7 +6100,7 @@
       <c r="E678" s="3"/>
       <c r="F678" s="3"/>
     </row>
-    <row r="679" ht="15.75" customHeight="1">
+    <row r="679" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -5994,7 +6108,7 @@
       <c r="E679" s="3"/>
       <c r="F679" s="3"/>
     </row>
-    <row r="680" ht="15.75" customHeight="1">
+    <row r="680" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -6002,7 +6116,7 @@
       <c r="E680" s="3"/>
       <c r="F680" s="3"/>
     </row>
-    <row r="681" ht="15.75" customHeight="1">
+    <row r="681" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -6010,7 +6124,7 @@
       <c r="E681" s="3"/>
       <c r="F681" s="3"/>
     </row>
-    <row r="682" ht="15.75" customHeight="1">
+    <row r="682" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -6018,7 +6132,7 @@
       <c r="E682" s="3"/>
       <c r="F682" s="3"/>
     </row>
-    <row r="683" ht="15.75" customHeight="1">
+    <row r="683" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -6026,7 +6140,7 @@
       <c r="E683" s="3"/>
       <c r="F683" s="3"/>
     </row>
-    <row r="684" ht="15.75" customHeight="1">
+    <row r="684" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -6034,7 +6148,7 @@
       <c r="E684" s="3"/>
       <c r="F684" s="3"/>
     </row>
-    <row r="685" ht="15.75" customHeight="1">
+    <row r="685" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -6042,7 +6156,7 @@
       <c r="E685" s="3"/>
       <c r="F685" s="3"/>
     </row>
-    <row r="686" ht="15.75" customHeight="1">
+    <row r="686" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -6050,7 +6164,7 @@
       <c r="E686" s="3"/>
       <c r="F686" s="3"/>
     </row>
-    <row r="687" ht="15.75" customHeight="1">
+    <row r="687" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -6058,7 +6172,7 @@
       <c r="E687" s="3"/>
       <c r="F687" s="3"/>
     </row>
-    <row r="688" ht="15.75" customHeight="1">
+    <row r="688" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -6066,7 +6180,7 @@
       <c r="E688" s="3"/>
       <c r="F688" s="3"/>
     </row>
-    <row r="689" ht="15.75" customHeight="1">
+    <row r="689" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -6074,7 +6188,7 @@
       <c r="E689" s="3"/>
       <c r="F689" s="3"/>
     </row>
-    <row r="690" ht="15.75" customHeight="1">
+    <row r="690" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -6082,7 +6196,7 @@
       <c r="E690" s="3"/>
       <c r="F690" s="3"/>
     </row>
-    <row r="691" ht="15.75" customHeight="1">
+    <row r="691" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -6090,7 +6204,7 @@
       <c r="E691" s="3"/>
       <c r="F691" s="3"/>
     </row>
-    <row r="692" ht="15.75" customHeight="1">
+    <row r="692" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -6098,7 +6212,7 @@
       <c r="E692" s="3"/>
       <c r="F692" s="3"/>
     </row>
-    <row r="693" ht="15.75" customHeight="1">
+    <row r="693" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -6106,7 +6220,7 @@
       <c r="E693" s="3"/>
       <c r="F693" s="3"/>
     </row>
-    <row r="694" ht="15.75" customHeight="1">
+    <row r="694" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -6114,7 +6228,7 @@
       <c r="E694" s="3"/>
       <c r="F694" s="3"/>
     </row>
-    <row r="695" ht="15.75" customHeight="1">
+    <row r="695" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -6122,7 +6236,7 @@
       <c r="E695" s="3"/>
       <c r="F695" s="3"/>
     </row>
-    <row r="696" ht="15.75" customHeight="1">
+    <row r="696" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -6130,7 +6244,7 @@
       <c r="E696" s="3"/>
       <c r="F696" s="3"/>
     </row>
-    <row r="697" ht="15.75" customHeight="1">
+    <row r="697" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -6138,7 +6252,7 @@
       <c r="E697" s="3"/>
       <c r="F697" s="3"/>
     </row>
-    <row r="698" ht="15.75" customHeight="1">
+    <row r="698" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -6146,7 +6260,7 @@
       <c r="E698" s="3"/>
       <c r="F698" s="3"/>
     </row>
-    <row r="699" ht="15.75" customHeight="1">
+    <row r="699" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -6154,7 +6268,7 @@
       <c r="E699" s="3"/>
       <c r="F699" s="3"/>
     </row>
-    <row r="700" ht="15.75" customHeight="1">
+    <row r="700" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -6162,7 +6276,7 @@
       <c r="E700" s="3"/>
       <c r="F700" s="3"/>
     </row>
-    <row r="701" ht="15.75" customHeight="1">
+    <row r="701" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -6170,7 +6284,7 @@
       <c r="E701" s="3"/>
       <c r="F701" s="3"/>
     </row>
-    <row r="702" ht="15.75" customHeight="1">
+    <row r="702" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -6178,7 +6292,7 @@
       <c r="E702" s="3"/>
       <c r="F702" s="3"/>
     </row>
-    <row r="703" ht="15.75" customHeight="1">
+    <row r="703" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -6186,7 +6300,7 @@
       <c r="E703" s="3"/>
       <c r="F703" s="3"/>
     </row>
-    <row r="704" ht="15.75" customHeight="1">
+    <row r="704" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -6194,7 +6308,7 @@
       <c r="E704" s="3"/>
       <c r="F704" s="3"/>
     </row>
-    <row r="705" ht="15.75" customHeight="1">
+    <row r="705" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -6202,7 +6316,7 @@
       <c r="E705" s="3"/>
       <c r="F705" s="3"/>
     </row>
-    <row r="706" ht="15.75" customHeight="1">
+    <row r="706" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -6210,7 +6324,7 @@
       <c r="E706" s="3"/>
       <c r="F706" s="3"/>
     </row>
-    <row r="707" ht="15.75" customHeight="1">
+    <row r="707" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -6218,7 +6332,7 @@
       <c r="E707" s="3"/>
       <c r="F707" s="3"/>
     </row>
-    <row r="708" ht="15.75" customHeight="1">
+    <row r="708" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -6226,7 +6340,7 @@
       <c r="E708" s="3"/>
       <c r="F708" s="3"/>
     </row>
-    <row r="709" ht="15.75" customHeight="1">
+    <row r="709" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -6234,7 +6348,7 @@
       <c r="E709" s="3"/>
       <c r="F709" s="3"/>
     </row>
-    <row r="710" ht="15.75" customHeight="1">
+    <row r="710" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -6242,7 +6356,7 @@
       <c r="E710" s="3"/>
       <c r="F710" s="3"/>
     </row>
-    <row r="711" ht="15.75" customHeight="1">
+    <row r="711" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -6250,7 +6364,7 @@
       <c r="E711" s="3"/>
       <c r="F711" s="3"/>
     </row>
-    <row r="712" ht="15.75" customHeight="1">
+    <row r="712" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -6258,7 +6372,7 @@
       <c r="E712" s="3"/>
       <c r="F712" s="3"/>
     </row>
-    <row r="713" ht="15.75" customHeight="1">
+    <row r="713" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -6266,7 +6380,7 @@
       <c r="E713" s="3"/>
       <c r="F713" s="3"/>
     </row>
-    <row r="714" ht="15.75" customHeight="1">
+    <row r="714" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -6274,7 +6388,7 @@
       <c r="E714" s="3"/>
       <c r="F714" s="3"/>
     </row>
-    <row r="715" ht="15.75" customHeight="1">
+    <row r="715" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -6282,7 +6396,7 @@
       <c r="E715" s="3"/>
       <c r="F715" s="3"/>
     </row>
-    <row r="716" ht="15.75" customHeight="1">
+    <row r="716" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -6290,7 +6404,7 @@
       <c r="E716" s="3"/>
       <c r="F716" s="3"/>
     </row>
-    <row r="717" ht="15.75" customHeight="1">
+    <row r="717" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -6298,7 +6412,7 @@
       <c r="E717" s="3"/>
       <c r="F717" s="3"/>
     </row>
-    <row r="718" ht="15.75" customHeight="1">
+    <row r="718" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -6306,7 +6420,7 @@
       <c r="E718" s="3"/>
       <c r="F718" s="3"/>
     </row>
-    <row r="719" ht="15.75" customHeight="1">
+    <row r="719" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -6314,7 +6428,7 @@
       <c r="E719" s="3"/>
       <c r="F719" s="3"/>
     </row>
-    <row r="720" ht="15.75" customHeight="1">
+    <row r="720" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -6322,7 +6436,7 @@
       <c r="E720" s="3"/>
       <c r="F720" s="3"/>
     </row>
-    <row r="721" ht="15.75" customHeight="1">
+    <row r="721" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -6330,7 +6444,7 @@
       <c r="E721" s="3"/>
       <c r="F721" s="3"/>
     </row>
-    <row r="722" ht="15.75" customHeight="1">
+    <row r="722" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -6338,7 +6452,7 @@
       <c r="E722" s="3"/>
       <c r="F722" s="3"/>
     </row>
-    <row r="723" ht="15.75" customHeight="1">
+    <row r="723" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -6346,7 +6460,7 @@
       <c r="E723" s="3"/>
       <c r="F723" s="3"/>
     </row>
-    <row r="724" ht="15.75" customHeight="1">
+    <row r="724" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -6354,7 +6468,7 @@
       <c r="E724" s="3"/>
       <c r="F724" s="3"/>
     </row>
-    <row r="725" ht="15.75" customHeight="1">
+    <row r="725" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -6362,7 +6476,7 @@
       <c r="E725" s="3"/>
       <c r="F725" s="3"/>
     </row>
-    <row r="726" ht="15.75" customHeight="1">
+    <row r="726" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -6370,7 +6484,7 @@
       <c r="E726" s="3"/>
       <c r="F726" s="3"/>
     </row>
-    <row r="727" ht="15.75" customHeight="1">
+    <row r="727" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -6378,7 +6492,7 @@
       <c r="E727" s="3"/>
       <c r="F727" s="3"/>
     </row>
-    <row r="728" ht="15.75" customHeight="1">
+    <row r="728" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -6386,7 +6500,7 @@
       <c r="E728" s="3"/>
       <c r="F728" s="3"/>
     </row>
-    <row r="729" ht="15.75" customHeight="1">
+    <row r="729" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -6394,7 +6508,7 @@
       <c r="E729" s="3"/>
       <c r="F729" s="3"/>
     </row>
-    <row r="730" ht="15.75" customHeight="1">
+    <row r="730" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -6402,7 +6516,7 @@
       <c r="E730" s="3"/>
       <c r="F730" s="3"/>
     </row>
-    <row r="731" ht="15.75" customHeight="1">
+    <row r="731" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -6410,7 +6524,7 @@
       <c r="E731" s="3"/>
       <c r="F731" s="3"/>
     </row>
-    <row r="732" ht="15.75" customHeight="1">
+    <row r="732" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -6418,7 +6532,7 @@
       <c r="E732" s="3"/>
       <c r="F732" s="3"/>
     </row>
-    <row r="733" ht="15.75" customHeight="1">
+    <row r="733" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -6426,7 +6540,7 @@
       <c r="E733" s="3"/>
       <c r="F733" s="3"/>
     </row>
-    <row r="734" ht="15.75" customHeight="1">
+    <row r="734" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -6434,7 +6548,7 @@
       <c r="E734" s="3"/>
       <c r="F734" s="3"/>
     </row>
-    <row r="735" ht="15.75" customHeight="1">
+    <row r="735" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -6442,7 +6556,7 @@
       <c r="E735" s="3"/>
       <c r="F735" s="3"/>
     </row>
-    <row r="736" ht="15.75" customHeight="1">
+    <row r="736" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -6450,7 +6564,7 @@
       <c r="E736" s="3"/>
       <c r="F736" s="3"/>
     </row>
-    <row r="737" ht="15.75" customHeight="1">
+    <row r="737" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -6458,7 +6572,7 @@
       <c r="E737" s="3"/>
       <c r="F737" s="3"/>
     </row>
-    <row r="738" ht="15.75" customHeight="1">
+    <row r="738" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -6466,7 +6580,7 @@
       <c r="E738" s="3"/>
       <c r="F738" s="3"/>
     </row>
-    <row r="739" ht="15.75" customHeight="1">
+    <row r="739" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -6474,7 +6588,7 @@
       <c r="E739" s="3"/>
       <c r="F739" s="3"/>
     </row>
-    <row r="740" ht="15.75" customHeight="1">
+    <row r="740" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -6482,7 +6596,7 @@
       <c r="E740" s="3"/>
       <c r="F740" s="3"/>
     </row>
-    <row r="741" ht="15.75" customHeight="1">
+    <row r="741" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -6490,7 +6604,7 @@
       <c r="E741" s="3"/>
       <c r="F741" s="3"/>
     </row>
-    <row r="742" ht="15.75" customHeight="1">
+    <row r="742" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -6498,7 +6612,7 @@
       <c r="E742" s="3"/>
       <c r="F742" s="3"/>
     </row>
-    <row r="743" ht="15.75" customHeight="1">
+    <row r="743" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -6506,7 +6620,7 @@
       <c r="E743" s="3"/>
       <c r="F743" s="3"/>
     </row>
-    <row r="744" ht="15.75" customHeight="1">
+    <row r="744" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -6514,7 +6628,7 @@
       <c r="E744" s="3"/>
       <c r="F744" s="3"/>
     </row>
-    <row r="745" ht="15.75" customHeight="1">
+    <row r="745" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -6522,7 +6636,7 @@
       <c r="E745" s="3"/>
       <c r="F745" s="3"/>
     </row>
-    <row r="746" ht="15.75" customHeight="1">
+    <row r="746" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -6530,7 +6644,7 @@
       <c r="E746" s="3"/>
       <c r="F746" s="3"/>
     </row>
-    <row r="747" ht="15.75" customHeight="1">
+    <row r="747" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -6538,7 +6652,7 @@
       <c r="E747" s="3"/>
       <c r="F747" s="3"/>
     </row>
-    <row r="748" ht="15.75" customHeight="1">
+    <row r="748" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -6546,7 +6660,7 @@
       <c r="E748" s="3"/>
       <c r="F748" s="3"/>
     </row>
-    <row r="749" ht="15.75" customHeight="1">
+    <row r="749" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -6554,7 +6668,7 @@
       <c r="E749" s="3"/>
       <c r="F749" s="3"/>
     </row>
-    <row r="750" ht="15.75" customHeight="1">
+    <row r="750" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -6562,7 +6676,7 @@
       <c r="E750" s="3"/>
       <c r="F750" s="3"/>
     </row>
-    <row r="751" ht="15.75" customHeight="1">
+    <row r="751" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -6570,7 +6684,7 @@
       <c r="E751" s="3"/>
       <c r="F751" s="3"/>
     </row>
-    <row r="752" ht="15.75" customHeight="1">
+    <row r="752" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -6578,7 +6692,7 @@
       <c r="E752" s="3"/>
       <c r="F752" s="3"/>
     </row>
-    <row r="753" ht="15.75" customHeight="1">
+    <row r="753" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -6586,7 +6700,7 @@
       <c r="E753" s="3"/>
       <c r="F753" s="3"/>
     </row>
-    <row r="754" ht="15.75" customHeight="1">
+    <row r="754" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -6594,7 +6708,7 @@
       <c r="E754" s="3"/>
       <c r="F754" s="3"/>
     </row>
-    <row r="755" ht="15.75" customHeight="1">
+    <row r="755" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -6602,7 +6716,7 @@
       <c r="E755" s="3"/>
       <c r="F755" s="3"/>
     </row>
-    <row r="756" ht="15.75" customHeight="1">
+    <row r="756" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -6610,7 +6724,7 @@
       <c r="E756" s="3"/>
       <c r="F756" s="3"/>
     </row>
-    <row r="757" ht="15.75" customHeight="1">
+    <row r="757" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -6618,7 +6732,7 @@
       <c r="E757" s="3"/>
       <c r="F757" s="3"/>
     </row>
-    <row r="758" ht="15.75" customHeight="1">
+    <row r="758" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -6626,7 +6740,7 @@
       <c r="E758" s="3"/>
       <c r="F758" s="3"/>
     </row>
-    <row r="759" ht="15.75" customHeight="1">
+    <row r="759" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -6634,7 +6748,7 @@
       <c r="E759" s="3"/>
       <c r="F759" s="3"/>
     </row>
-    <row r="760" ht="15.75" customHeight="1">
+    <row r="760" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -6642,7 +6756,7 @@
       <c r="E760" s="3"/>
       <c r="F760" s="3"/>
     </row>
-    <row r="761" ht="15.75" customHeight="1">
+    <row r="761" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -6650,7 +6764,7 @@
       <c r="E761" s="3"/>
       <c r="F761" s="3"/>
     </row>
-    <row r="762" ht="15.75" customHeight="1">
+    <row r="762" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -6658,7 +6772,7 @@
       <c r="E762" s="3"/>
       <c r="F762" s="3"/>
     </row>
-    <row r="763" ht="15.75" customHeight="1">
+    <row r="763" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -6666,7 +6780,7 @@
       <c r="E763" s="3"/>
       <c r="F763" s="3"/>
     </row>
-    <row r="764" ht="15.75" customHeight="1">
+    <row r="764" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -6674,7 +6788,7 @@
       <c r="E764" s="3"/>
       <c r="F764" s="3"/>
     </row>
-    <row r="765" ht="15.75" customHeight="1">
+    <row r="765" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -6682,7 +6796,7 @@
       <c r="E765" s="3"/>
       <c r="F765" s="3"/>
     </row>
-    <row r="766" ht="15.75" customHeight="1">
+    <row r="766" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -6690,7 +6804,7 @@
       <c r="E766" s="3"/>
       <c r="F766" s="3"/>
     </row>
-    <row r="767" ht="15.75" customHeight="1">
+    <row r="767" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -6698,7 +6812,7 @@
       <c r="E767" s="3"/>
       <c r="F767" s="3"/>
     </row>
-    <row r="768" ht="15.75" customHeight="1">
+    <row r="768" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -6706,7 +6820,7 @@
       <c r="E768" s="3"/>
       <c r="F768" s="3"/>
     </row>
-    <row r="769" ht="15.75" customHeight="1">
+    <row r="769" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -6714,7 +6828,7 @@
       <c r="E769" s="3"/>
       <c r="F769" s="3"/>
     </row>
-    <row r="770" ht="15.75" customHeight="1">
+    <row r="770" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -6722,7 +6836,7 @@
       <c r="E770" s="3"/>
       <c r="F770" s="3"/>
     </row>
-    <row r="771" ht="15.75" customHeight="1">
+    <row r="771" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -6730,7 +6844,7 @@
       <c r="E771" s="3"/>
       <c r="F771" s="3"/>
     </row>
-    <row r="772" ht="15.75" customHeight="1">
+    <row r="772" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -6738,7 +6852,7 @@
       <c r="E772" s="3"/>
       <c r="F772" s="3"/>
     </row>
-    <row r="773" ht="15.75" customHeight="1">
+    <row r="773" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -6746,7 +6860,7 @@
       <c r="E773" s="3"/>
       <c r="F773" s="3"/>
     </row>
-    <row r="774" ht="15.75" customHeight="1">
+    <row r="774" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -6754,7 +6868,7 @@
       <c r="E774" s="3"/>
       <c r="F774" s="3"/>
     </row>
-    <row r="775" ht="15.75" customHeight="1">
+    <row r="775" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -6762,7 +6876,7 @@
       <c r="E775" s="3"/>
       <c r="F775" s="3"/>
     </row>
-    <row r="776" ht="15.75" customHeight="1">
+    <row r="776" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -6770,7 +6884,7 @@
       <c r="E776" s="3"/>
       <c r="F776" s="3"/>
     </row>
-    <row r="777" ht="15.75" customHeight="1">
+    <row r="777" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -6778,7 +6892,7 @@
       <c r="E777" s="3"/>
       <c r="F777" s="3"/>
     </row>
-    <row r="778" ht="15.75" customHeight="1">
+    <row r="778" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -6786,7 +6900,7 @@
       <c r="E778" s="3"/>
       <c r="F778" s="3"/>
     </row>
-    <row r="779" ht="15.75" customHeight="1">
+    <row r="779" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -6794,7 +6908,7 @@
       <c r="E779" s="3"/>
       <c r="F779" s="3"/>
     </row>
-    <row r="780" ht="15.75" customHeight="1">
+    <row r="780" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -6802,7 +6916,7 @@
       <c r="E780" s="3"/>
       <c r="F780" s="3"/>
     </row>
-    <row r="781" ht="15.75" customHeight="1">
+    <row r="781" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -6810,7 +6924,7 @@
       <c r="E781" s="3"/>
       <c r="F781" s="3"/>
     </row>
-    <row r="782" ht="15.75" customHeight="1">
+    <row r="782" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -6818,7 +6932,7 @@
       <c r="E782" s="3"/>
       <c r="F782" s="3"/>
     </row>
-    <row r="783" ht="15.75" customHeight="1">
+    <row r="783" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -6826,7 +6940,7 @@
       <c r="E783" s="3"/>
       <c r="F783" s="3"/>
     </row>
-    <row r="784" ht="15.75" customHeight="1">
+    <row r="784" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -6834,7 +6948,7 @@
       <c r="E784" s="3"/>
       <c r="F784" s="3"/>
     </row>
-    <row r="785" ht="15.75" customHeight="1">
+    <row r="785" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -6842,7 +6956,7 @@
       <c r="E785" s="3"/>
       <c r="F785" s="3"/>
     </row>
-    <row r="786" ht="15.75" customHeight="1">
+    <row r="786" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -6850,7 +6964,7 @@
       <c r="E786" s="3"/>
       <c r="F786" s="3"/>
     </row>
-    <row r="787" ht="15.75" customHeight="1">
+    <row r="787" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -6858,7 +6972,7 @@
       <c r="E787" s="3"/>
       <c r="F787" s="3"/>
     </row>
-    <row r="788" ht="15.75" customHeight="1">
+    <row r="788" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -6866,7 +6980,7 @@
       <c r="E788" s="3"/>
       <c r="F788" s="3"/>
     </row>
-    <row r="789" ht="15.75" customHeight="1">
+    <row r="789" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -6874,7 +6988,7 @@
       <c r="E789" s="3"/>
       <c r="F789" s="3"/>
     </row>
-    <row r="790" ht="15.75" customHeight="1">
+    <row r="790" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -6882,7 +6996,7 @@
       <c r="E790" s="3"/>
       <c r="F790" s="3"/>
     </row>
-    <row r="791" ht="15.75" customHeight="1">
+    <row r="791" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -6890,7 +7004,7 @@
       <c r="E791" s="3"/>
       <c r="F791" s="3"/>
     </row>
-    <row r="792" ht="15.75" customHeight="1">
+    <row r="792" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -6898,7 +7012,7 @@
       <c r="E792" s="3"/>
       <c r="F792" s="3"/>
     </row>
-    <row r="793" ht="15.75" customHeight="1">
+    <row r="793" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -6906,7 +7020,7 @@
       <c r="E793" s="3"/>
       <c r="F793" s="3"/>
     </row>
-    <row r="794" ht="15.75" customHeight="1">
+    <row r="794" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -6914,7 +7028,7 @@
       <c r="E794" s="3"/>
       <c r="F794" s="3"/>
     </row>
-    <row r="795" ht="15.75" customHeight="1">
+    <row r="795" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -6922,7 +7036,7 @@
       <c r="E795" s="3"/>
       <c r="F795" s="3"/>
     </row>
-    <row r="796" ht="15.75" customHeight="1">
+    <row r="796" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -6930,7 +7044,7 @@
       <c r="E796" s="3"/>
       <c r="F796" s="3"/>
     </row>
-    <row r="797" ht="15.75" customHeight="1">
+    <row r="797" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -6938,7 +7052,7 @@
       <c r="E797" s="3"/>
       <c r="F797" s="3"/>
     </row>
-    <row r="798" ht="15.75" customHeight="1">
+    <row r="798" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -6946,7 +7060,7 @@
       <c r="E798" s="3"/>
       <c r="F798" s="3"/>
     </row>
-    <row r="799" ht="15.75" customHeight="1">
+    <row r="799" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -6954,7 +7068,7 @@
       <c r="E799" s="3"/>
       <c r="F799" s="3"/>
     </row>
-    <row r="800" ht="15.75" customHeight="1">
+    <row r="800" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -6962,7 +7076,7 @@
       <c r="E800" s="3"/>
       <c r="F800" s="3"/>
     </row>
-    <row r="801" ht="15.75" customHeight="1">
+    <row r="801" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -6970,7 +7084,7 @@
       <c r="E801" s="3"/>
       <c r="F801" s="3"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
+    <row r="802" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -6978,7 +7092,7 @@
       <c r="E802" s="3"/>
       <c r="F802" s="3"/>
     </row>
-    <row r="803" ht="15.75" customHeight="1">
+    <row r="803" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -6986,7 +7100,7 @@
       <c r="E803" s="3"/>
       <c r="F803" s="3"/>
     </row>
-    <row r="804" ht="15.75" customHeight="1">
+    <row r="804" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -6994,7 +7108,7 @@
       <c r="E804" s="3"/>
       <c r="F804" s="3"/>
     </row>
-    <row r="805" ht="15.75" customHeight="1">
+    <row r="805" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -7002,7 +7116,7 @@
       <c r="E805" s="3"/>
       <c r="F805" s="3"/>
     </row>
-    <row r="806" ht="15.75" customHeight="1">
+    <row r="806" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -7010,7 +7124,7 @@
       <c r="E806" s="3"/>
       <c r="F806" s="3"/>
     </row>
-    <row r="807" ht="15.75" customHeight="1">
+    <row r="807" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -7018,7 +7132,7 @@
       <c r="E807" s="3"/>
       <c r="F807" s="3"/>
     </row>
-    <row r="808" ht="15.75" customHeight="1">
+    <row r="808" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -7026,7 +7140,7 @@
       <c r="E808" s="3"/>
       <c r="F808" s="3"/>
     </row>
-    <row r="809" ht="15.75" customHeight="1">
+    <row r="809" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -7034,7 +7148,7 @@
       <c r="E809" s="3"/>
       <c r="F809" s="3"/>
     </row>
-    <row r="810" ht="15.75" customHeight="1">
+    <row r="810" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -7042,7 +7156,7 @@
       <c r="E810" s="3"/>
       <c r="F810" s="3"/>
     </row>
-    <row r="811" ht="15.75" customHeight="1">
+    <row r="811" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -7050,7 +7164,7 @@
       <c r="E811" s="3"/>
       <c r="F811" s="3"/>
     </row>
-    <row r="812" ht="15.75" customHeight="1">
+    <row r="812" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -7058,7 +7172,7 @@
       <c r="E812" s="3"/>
       <c r="F812" s="3"/>
     </row>
-    <row r="813" ht="15.75" customHeight="1">
+    <row r="813" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -7066,7 +7180,7 @@
       <c r="E813" s="3"/>
       <c r="F813" s="3"/>
     </row>
-    <row r="814" ht="15.75" customHeight="1">
+    <row r="814" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -7074,7 +7188,7 @@
       <c r="E814" s="3"/>
       <c r="F814" s="3"/>
     </row>
-    <row r="815" ht="15.75" customHeight="1">
+    <row r="815" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -7082,7 +7196,7 @@
       <c r="E815" s="3"/>
       <c r="F815" s="3"/>
     </row>
-    <row r="816" ht="15.75" customHeight="1">
+    <row r="816" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -7090,7 +7204,7 @@
       <c r="E816" s="3"/>
       <c r="F816" s="3"/>
     </row>
-    <row r="817" ht="15.75" customHeight="1">
+    <row r="817" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -7098,7 +7212,7 @@
       <c r="E817" s="3"/>
       <c r="F817" s="3"/>
     </row>
-    <row r="818" ht="15.75" customHeight="1">
+    <row r="818" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -7106,7 +7220,7 @@
       <c r="E818" s="3"/>
       <c r="F818" s="3"/>
     </row>
-    <row r="819" ht="15.75" customHeight="1">
+    <row r="819" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -7114,7 +7228,7 @@
       <c r="E819" s="3"/>
       <c r="F819" s="3"/>
     </row>
-    <row r="820" ht="15.75" customHeight="1">
+    <row r="820" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -7122,7 +7236,7 @@
       <c r="E820" s="3"/>
       <c r="F820" s="3"/>
     </row>
-    <row r="821" ht="15.75" customHeight="1">
+    <row r="821" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -7130,7 +7244,7 @@
       <c r="E821" s="3"/>
       <c r="F821" s="3"/>
     </row>
-    <row r="822" ht="15.75" customHeight="1">
+    <row r="822" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -7138,7 +7252,7 @@
       <c r="E822" s="3"/>
       <c r="F822" s="3"/>
     </row>
-    <row r="823" ht="15.75" customHeight="1">
+    <row r="823" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -7146,7 +7260,7 @@
       <c r="E823" s="3"/>
       <c r="F823" s="3"/>
     </row>
-    <row r="824" ht="15.75" customHeight="1">
+    <row r="824" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -7154,7 +7268,7 @@
       <c r="E824" s="3"/>
       <c r="F824" s="3"/>
     </row>
-    <row r="825" ht="15.75" customHeight="1">
+    <row r="825" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -7162,7 +7276,7 @@
       <c r="E825" s="3"/>
       <c r="F825" s="3"/>
     </row>
-    <row r="826" ht="15.75" customHeight="1">
+    <row r="826" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -7170,7 +7284,7 @@
       <c r="E826" s="3"/>
       <c r="F826" s="3"/>
     </row>
-    <row r="827" ht="15.75" customHeight="1">
+    <row r="827" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -7178,7 +7292,7 @@
       <c r="E827" s="3"/>
       <c r="F827" s="3"/>
     </row>
-    <row r="828" ht="15.75" customHeight="1">
+    <row r="828" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -7186,7 +7300,7 @@
       <c r="E828" s="3"/>
       <c r="F828" s="3"/>
     </row>
-    <row r="829" ht="15.75" customHeight="1">
+    <row r="829" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -7194,7 +7308,7 @@
       <c r="E829" s="3"/>
       <c r="F829" s="3"/>
     </row>
-    <row r="830" ht="15.75" customHeight="1">
+    <row r="830" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -7202,7 +7316,7 @@
       <c r="E830" s="3"/>
       <c r="F830" s="3"/>
     </row>
-    <row r="831" ht="15.75" customHeight="1">
+    <row r="831" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -7210,7 +7324,7 @@
       <c r="E831" s="3"/>
       <c r="F831" s="3"/>
     </row>
-    <row r="832" ht="15.75" customHeight="1">
+    <row r="832" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -7218,7 +7332,7 @@
       <c r="E832" s="3"/>
       <c r="F832" s="3"/>
     </row>
-    <row r="833" ht="15.75" customHeight="1">
+    <row r="833" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -7226,7 +7340,7 @@
       <c r="E833" s="3"/>
       <c r="F833" s="3"/>
     </row>
-    <row r="834" ht="15.75" customHeight="1">
+    <row r="834" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -7234,7 +7348,7 @@
       <c r="E834" s="3"/>
       <c r="F834" s="3"/>
     </row>
-    <row r="835" ht="15.75" customHeight="1">
+    <row r="835" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -7242,7 +7356,7 @@
       <c r="E835" s="3"/>
       <c r="F835" s="3"/>
     </row>
-    <row r="836" ht="15.75" customHeight="1">
+    <row r="836" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -7250,7 +7364,7 @@
       <c r="E836" s="3"/>
       <c r="F836" s="3"/>
     </row>
-    <row r="837" ht="15.75" customHeight="1">
+    <row r="837" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -7258,7 +7372,7 @@
       <c r="E837" s="3"/>
       <c r="F837" s="3"/>
     </row>
-    <row r="838" ht="15.75" customHeight="1">
+    <row r="838" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -7266,7 +7380,7 @@
       <c r="E838" s="3"/>
       <c r="F838" s="3"/>
     </row>
-    <row r="839" ht="15.75" customHeight="1">
+    <row r="839" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -7274,7 +7388,7 @@
       <c r="E839" s="3"/>
       <c r="F839" s="3"/>
     </row>
-    <row r="840" ht="15.75" customHeight="1">
+    <row r="840" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -7282,7 +7396,7 @@
       <c r="E840" s="3"/>
       <c r="F840" s="3"/>
     </row>
-    <row r="841" ht="15.75" customHeight="1">
+    <row r="841" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -7290,7 +7404,7 @@
       <c r="E841" s="3"/>
       <c r="F841" s="3"/>
     </row>
-    <row r="842" ht="15.75" customHeight="1">
+    <row r="842" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -7298,7 +7412,7 @@
       <c r="E842" s="3"/>
       <c r="F842" s="3"/>
     </row>
-    <row r="843" ht="15.75" customHeight="1">
+    <row r="843" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -7306,7 +7420,7 @@
       <c r="E843" s="3"/>
       <c r="F843" s="3"/>
     </row>
-    <row r="844" ht="15.75" customHeight="1">
+    <row r="844" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -7314,7 +7428,7 @@
       <c r="E844" s="3"/>
       <c r="F844" s="3"/>
     </row>
-    <row r="845" ht="15.75" customHeight="1">
+    <row r="845" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -7322,7 +7436,7 @@
       <c r="E845" s="3"/>
       <c r="F845" s="3"/>
     </row>
-    <row r="846" ht="15.75" customHeight="1">
+    <row r="846" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -7330,7 +7444,7 @@
       <c r="E846" s="3"/>
       <c r="F846" s="3"/>
     </row>
-    <row r="847" ht="15.75" customHeight="1">
+    <row r="847" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -7338,7 +7452,7 @@
       <c r="E847" s="3"/>
       <c r="F847" s="3"/>
     </row>
-    <row r="848" ht="15.75" customHeight="1">
+    <row r="848" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -7346,7 +7460,7 @@
       <c r="E848" s="3"/>
       <c r="F848" s="3"/>
     </row>
-    <row r="849" ht="15.75" customHeight="1">
+    <row r="849" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -7354,7 +7468,7 @@
       <c r="E849" s="3"/>
       <c r="F849" s="3"/>
     </row>
-    <row r="850" ht="15.75" customHeight="1">
+    <row r="850" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -7362,7 +7476,7 @@
       <c r="E850" s="3"/>
       <c r="F850" s="3"/>
     </row>
-    <row r="851" ht="15.75" customHeight="1">
+    <row r="851" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -7370,7 +7484,7 @@
       <c r="E851" s="3"/>
       <c r="F851" s="3"/>
     </row>
-    <row r="852" ht="15.75" customHeight="1">
+    <row r="852" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -7378,7 +7492,7 @@
       <c r="E852" s="3"/>
       <c r="F852" s="3"/>
     </row>
-    <row r="853" ht="15.75" customHeight="1">
+    <row r="853" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -7386,7 +7500,7 @@
       <c r="E853" s="3"/>
       <c r="F853" s="3"/>
     </row>
-    <row r="854" ht="15.75" customHeight="1">
+    <row r="854" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -7394,7 +7508,7 @@
       <c r="E854" s="3"/>
       <c r="F854" s="3"/>
     </row>
-    <row r="855" ht="15.75" customHeight="1">
+    <row r="855" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -7402,7 +7516,7 @@
       <c r="E855" s="3"/>
       <c r="F855" s="3"/>
     </row>
-    <row r="856" ht="15.75" customHeight="1">
+    <row r="856" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -7410,7 +7524,7 @@
       <c r="E856" s="3"/>
       <c r="F856" s="3"/>
     </row>
-    <row r="857" ht="15.75" customHeight="1">
+    <row r="857" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -7418,7 +7532,7 @@
       <c r="E857" s="3"/>
       <c r="F857" s="3"/>
     </row>
-    <row r="858" ht="15.75" customHeight="1">
+    <row r="858" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -7426,7 +7540,7 @@
       <c r="E858" s="3"/>
       <c r="F858" s="3"/>
     </row>
-    <row r="859" ht="15.75" customHeight="1">
+    <row r="859" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -7434,7 +7548,7 @@
       <c r="E859" s="3"/>
       <c r="F859" s="3"/>
     </row>
-    <row r="860" ht="15.75" customHeight="1">
+    <row r="860" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -7442,7 +7556,7 @@
       <c r="E860" s="3"/>
       <c r="F860" s="3"/>
     </row>
-    <row r="861" ht="15.75" customHeight="1">
+    <row r="861" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -7450,7 +7564,7 @@
       <c r="E861" s="3"/>
       <c r="F861" s="3"/>
     </row>
-    <row r="862" ht="15.75" customHeight="1">
+    <row r="862" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -7458,7 +7572,7 @@
       <c r="E862" s="3"/>
       <c r="F862" s="3"/>
     </row>
-    <row r="863" ht="15.75" customHeight="1">
+    <row r="863" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -7466,7 +7580,7 @@
       <c r="E863" s="3"/>
       <c r="F863" s="3"/>
     </row>
-    <row r="864" ht="15.75" customHeight="1">
+    <row r="864" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -7474,7 +7588,7 @@
       <c r="E864" s="3"/>
       <c r="F864" s="3"/>
     </row>
-    <row r="865" ht="15.75" customHeight="1">
+    <row r="865" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -7482,7 +7596,7 @@
       <c r="E865" s="3"/>
       <c r="F865" s="3"/>
     </row>
-    <row r="866" ht="15.75" customHeight="1">
+    <row r="866" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -7490,7 +7604,7 @@
       <c r="E866" s="3"/>
       <c r="F866" s="3"/>
     </row>
-    <row r="867" ht="15.75" customHeight="1">
+    <row r="867" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -7498,7 +7612,7 @@
       <c r="E867" s="3"/>
       <c r="F867" s="3"/>
     </row>
-    <row r="868" ht="15.75" customHeight="1">
+    <row r="868" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -7506,7 +7620,7 @@
       <c r="E868" s="3"/>
       <c r="F868" s="3"/>
     </row>
-    <row r="869" ht="15.75" customHeight="1">
+    <row r="869" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -7514,7 +7628,7 @@
       <c r="E869" s="3"/>
       <c r="F869" s="3"/>
     </row>
-    <row r="870" ht="15.75" customHeight="1">
+    <row r="870" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -7522,7 +7636,7 @@
       <c r="E870" s="3"/>
       <c r="F870" s="3"/>
     </row>
-    <row r="871" ht="15.75" customHeight="1">
+    <row r="871" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -7530,7 +7644,7 @@
       <c r="E871" s="3"/>
       <c r="F871" s="3"/>
     </row>
-    <row r="872" ht="15.75" customHeight="1">
+    <row r="872" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -7538,7 +7652,7 @@
       <c r="E872" s="3"/>
       <c r="F872" s="3"/>
     </row>
-    <row r="873" ht="15.75" customHeight="1">
+    <row r="873" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -7546,7 +7660,7 @@
       <c r="E873" s="3"/>
       <c r="F873" s="3"/>
     </row>
-    <row r="874" ht="15.75" customHeight="1">
+    <row r="874" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -7554,7 +7668,7 @@
       <c r="E874" s="3"/>
       <c r="F874" s="3"/>
     </row>
-    <row r="875" ht="15.75" customHeight="1">
+    <row r="875" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -7562,7 +7676,7 @@
       <c r="E875" s="3"/>
       <c r="F875" s="3"/>
     </row>
-    <row r="876" ht="15.75" customHeight="1">
+    <row r="876" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -7570,7 +7684,7 @@
       <c r="E876" s="3"/>
       <c r="F876" s="3"/>
     </row>
-    <row r="877" ht="15.75" customHeight="1">
+    <row r="877" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -7578,7 +7692,7 @@
       <c r="E877" s="3"/>
       <c r="F877" s="3"/>
     </row>
-    <row r="878" ht="15.75" customHeight="1">
+    <row r="878" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -7586,7 +7700,7 @@
       <c r="E878" s="3"/>
       <c r="F878" s="3"/>
     </row>
-    <row r="879" ht="15.75" customHeight="1">
+    <row r="879" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -7594,7 +7708,7 @@
       <c r="E879" s="3"/>
       <c r="F879" s="3"/>
     </row>
-    <row r="880" ht="15.75" customHeight="1">
+    <row r="880" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -7602,7 +7716,7 @@
       <c r="E880" s="3"/>
       <c r="F880" s="3"/>
     </row>
-    <row r="881" ht="15.75" customHeight="1">
+    <row r="881" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -7610,7 +7724,7 @@
       <c r="E881" s="3"/>
       <c r="F881" s="3"/>
     </row>
-    <row r="882" ht="15.75" customHeight="1">
+    <row r="882" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -7618,7 +7732,7 @@
       <c r="E882" s="3"/>
       <c r="F882" s="3"/>
     </row>
-    <row r="883" ht="15.75" customHeight="1">
+    <row r="883" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -7626,7 +7740,7 @@
       <c r="E883" s="3"/>
       <c r="F883" s="3"/>
     </row>
-    <row r="884" ht="15.75" customHeight="1">
+    <row r="884" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -7634,7 +7748,7 @@
       <c r="E884" s="3"/>
       <c r="F884" s="3"/>
     </row>
-    <row r="885" ht="15.75" customHeight="1">
+    <row r="885" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -7642,7 +7756,7 @@
       <c r="E885" s="3"/>
       <c r="F885" s="3"/>
     </row>
-    <row r="886" ht="15.75" customHeight="1">
+    <row r="886" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -7650,7 +7764,7 @@
       <c r="E886" s="3"/>
       <c r="F886" s="3"/>
     </row>
-    <row r="887" ht="15.75" customHeight="1">
+    <row r="887" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -7658,7 +7772,7 @@
       <c r="E887" s="3"/>
       <c r="F887" s="3"/>
     </row>
-    <row r="888" ht="15.75" customHeight="1">
+    <row r="888" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -7666,7 +7780,7 @@
       <c r="E888" s="3"/>
       <c r="F888" s="3"/>
     </row>
-    <row r="889" ht="15.75" customHeight="1">
+    <row r="889" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -7674,7 +7788,7 @@
       <c r="E889" s="3"/>
       <c r="F889" s="3"/>
     </row>
-    <row r="890" ht="15.75" customHeight="1">
+    <row r="890" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -7682,7 +7796,7 @@
       <c r="E890" s="3"/>
       <c r="F890" s="3"/>
     </row>
-    <row r="891" ht="15.75" customHeight="1">
+    <row r="891" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -7690,7 +7804,7 @@
       <c r="E891" s="3"/>
       <c r="F891" s="3"/>
     </row>
-    <row r="892" ht="15.75" customHeight="1">
+    <row r="892" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -7698,7 +7812,7 @@
       <c r="E892" s="3"/>
       <c r="F892" s="3"/>
     </row>
-    <row r="893" ht="15.75" customHeight="1">
+    <row r="893" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -7706,7 +7820,7 @@
       <c r="E893" s="3"/>
       <c r="F893" s="3"/>
     </row>
-    <row r="894" ht="15.75" customHeight="1">
+    <row r="894" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -7714,7 +7828,7 @@
       <c r="E894" s="3"/>
       <c r="F894" s="3"/>
     </row>
-    <row r="895" ht="15.75" customHeight="1">
+    <row r="895" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -7722,7 +7836,7 @@
       <c r="E895" s="3"/>
       <c r="F895" s="3"/>
     </row>
-    <row r="896" ht="15.75" customHeight="1">
+    <row r="896" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -7730,7 +7844,7 @@
       <c r="E896" s="3"/>
       <c r="F896" s="3"/>
     </row>
-    <row r="897" ht="15.75" customHeight="1">
+    <row r="897" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -7738,7 +7852,7 @@
       <c r="E897" s="3"/>
       <c r="F897" s="3"/>
     </row>
-    <row r="898" ht="15.75" customHeight="1">
+    <row r="898" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -7746,7 +7860,7 @@
       <c r="E898" s="3"/>
       <c r="F898" s="3"/>
     </row>
-    <row r="899" ht="15.75" customHeight="1">
+    <row r="899" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -7754,7 +7868,7 @@
       <c r="E899" s="3"/>
       <c r="F899" s="3"/>
     </row>
-    <row r="900" ht="15.75" customHeight="1">
+    <row r="900" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -7762,7 +7876,7 @@
       <c r="E900" s="3"/>
       <c r="F900" s="3"/>
     </row>
-    <row r="901" ht="15.75" customHeight="1">
+    <row r="901" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -7770,7 +7884,7 @@
       <c r="E901" s="3"/>
       <c r="F901" s="3"/>
     </row>
-    <row r="902" ht="15.75" customHeight="1">
+    <row r="902" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -7778,7 +7892,7 @@
       <c r="E902" s="3"/>
       <c r="F902" s="3"/>
     </row>
-    <row r="903" ht="15.75" customHeight="1">
+    <row r="903" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -7786,7 +7900,7 @@
       <c r="E903" s="3"/>
       <c r="F903" s="3"/>
     </row>
-    <row r="904" ht="15.75" customHeight="1">
+    <row r="904" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -7794,7 +7908,7 @@
       <c r="E904" s="3"/>
       <c r="F904" s="3"/>
     </row>
-    <row r="905" ht="15.75" customHeight="1">
+    <row r="905" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -7802,7 +7916,7 @@
       <c r="E905" s="3"/>
       <c r="F905" s="3"/>
     </row>
-    <row r="906" ht="15.75" customHeight="1">
+    <row r="906" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -7810,7 +7924,7 @@
       <c r="E906" s="3"/>
       <c r="F906" s="3"/>
     </row>
-    <row r="907" ht="15.75" customHeight="1">
+    <row r="907" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -7818,7 +7932,7 @@
       <c r="E907" s="3"/>
       <c r="F907" s="3"/>
     </row>
-    <row r="908" ht="15.75" customHeight="1">
+    <row r="908" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -7826,7 +7940,7 @@
       <c r="E908" s="3"/>
       <c r="F908" s="3"/>
     </row>
-    <row r="909" ht="15.75" customHeight="1">
+    <row r="909" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -7834,7 +7948,7 @@
       <c r="E909" s="3"/>
       <c r="F909" s="3"/>
     </row>
-    <row r="910" ht="15.75" customHeight="1">
+    <row r="910" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -7842,7 +7956,7 @@
       <c r="E910" s="3"/>
       <c r="F910" s="3"/>
     </row>
-    <row r="911" ht="15.75" customHeight="1">
+    <row r="911" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -7850,7 +7964,7 @@
       <c r="E911" s="3"/>
       <c r="F911" s="3"/>
     </row>
-    <row r="912" ht="15.75" customHeight="1">
+    <row r="912" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -7858,7 +7972,7 @@
       <c r="E912" s="3"/>
       <c r="F912" s="3"/>
     </row>
-    <row r="913" ht="15.75" customHeight="1">
+    <row r="913" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -7866,7 +7980,7 @@
       <c r="E913" s="3"/>
       <c r="F913" s="3"/>
     </row>
-    <row r="914" ht="15.75" customHeight="1">
+    <row r="914" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -7874,7 +7988,7 @@
       <c r="E914" s="3"/>
       <c r="F914" s="3"/>
     </row>
-    <row r="915" ht="15.75" customHeight="1">
+    <row r="915" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -7882,7 +7996,7 @@
       <c r="E915" s="3"/>
       <c r="F915" s="3"/>
     </row>
-    <row r="916" ht="15.75" customHeight="1">
+    <row r="916" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -7890,7 +8004,7 @@
       <c r="E916" s="3"/>
       <c r="F916" s="3"/>
     </row>
-    <row r="917" ht="15.75" customHeight="1">
+    <row r="917" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -7898,7 +8012,7 @@
       <c r="E917" s="3"/>
       <c r="F917" s="3"/>
     </row>
-    <row r="918" ht="15.75" customHeight="1">
+    <row r="918" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -7906,7 +8020,7 @@
       <c r="E918" s="3"/>
       <c r="F918" s="3"/>
     </row>
-    <row r="919" ht="15.75" customHeight="1">
+    <row r="919" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -7914,7 +8028,7 @@
       <c r="E919" s="3"/>
       <c r="F919" s="3"/>
     </row>
-    <row r="920" ht="15.75" customHeight="1">
+    <row r="920" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -7922,7 +8036,7 @@
       <c r="E920" s="3"/>
       <c r="F920" s="3"/>
     </row>
-    <row r="921" ht="15.75" customHeight="1">
+    <row r="921" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -7930,7 +8044,7 @@
       <c r="E921" s="3"/>
       <c r="F921" s="3"/>
     </row>
-    <row r="922" ht="15.75" customHeight="1">
+    <row r="922" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -7938,7 +8052,7 @@
       <c r="E922" s="3"/>
       <c r="F922" s="3"/>
     </row>
-    <row r="923" ht="15.75" customHeight="1">
+    <row r="923" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -7946,7 +8060,7 @@
       <c r="E923" s="3"/>
       <c r="F923" s="3"/>
     </row>
-    <row r="924" ht="15.75" customHeight="1">
+    <row r="924" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -7954,7 +8068,7 @@
       <c r="E924" s="3"/>
       <c r="F924" s="3"/>
     </row>
-    <row r="925" ht="15.75" customHeight="1">
+    <row r="925" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -7962,7 +8076,7 @@
       <c r="E925" s="3"/>
       <c r="F925" s="3"/>
     </row>
-    <row r="926" ht="15.75" customHeight="1">
+    <row r="926" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -7970,7 +8084,7 @@
       <c r="E926" s="3"/>
       <c r="F926" s="3"/>
     </row>
-    <row r="927" ht="15.75" customHeight="1">
+    <row r="927" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -7978,7 +8092,7 @@
       <c r="E927" s="3"/>
       <c r="F927" s="3"/>
     </row>
-    <row r="928" ht="15.75" customHeight="1">
+    <row r="928" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -7986,7 +8100,7 @@
       <c r="E928" s="3"/>
       <c r="F928" s="3"/>
     </row>
-    <row r="929" ht="15.75" customHeight="1">
+    <row r="929" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -7994,7 +8108,7 @@
       <c r="E929" s="3"/>
       <c r="F929" s="3"/>
     </row>
-    <row r="930" ht="15.75" customHeight="1">
+    <row r="930" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -8002,7 +8116,7 @@
       <c r="E930" s="3"/>
       <c r="F930" s="3"/>
     </row>
-    <row r="931" ht="15.75" customHeight="1">
+    <row r="931" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -8010,7 +8124,7 @@
       <c r="E931" s="3"/>
       <c r="F931" s="3"/>
     </row>
-    <row r="932" ht="15.75" customHeight="1">
+    <row r="932" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -8018,7 +8132,7 @@
       <c r="E932" s="3"/>
       <c r="F932" s="3"/>
     </row>
-    <row r="933" ht="15.75" customHeight="1">
+    <row r="933" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -8026,7 +8140,7 @@
       <c r="E933" s="3"/>
       <c r="F933" s="3"/>
     </row>
-    <row r="934" ht="15.75" customHeight="1">
+    <row r="934" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -8034,7 +8148,7 @@
       <c r="E934" s="3"/>
       <c r="F934" s="3"/>
     </row>
-    <row r="935" ht="15.75" customHeight="1">
+    <row r="935" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -8042,7 +8156,7 @@
       <c r="E935" s="3"/>
       <c r="F935" s="3"/>
     </row>
-    <row r="936" ht="15.75" customHeight="1">
+    <row r="936" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -8050,7 +8164,7 @@
       <c r="E936" s="3"/>
       <c r="F936" s="3"/>
     </row>
-    <row r="937" ht="15.75" customHeight="1">
+    <row r="937" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -8058,7 +8172,7 @@
       <c r="E937" s="3"/>
       <c r="F937" s="3"/>
     </row>
-    <row r="938" ht="15.75" customHeight="1">
+    <row r="938" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -8066,7 +8180,7 @@
       <c r="E938" s="3"/>
       <c r="F938" s="3"/>
     </row>
-    <row r="939" ht="15.75" customHeight="1">
+    <row r="939" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -8074,7 +8188,7 @@
       <c r="E939" s="3"/>
       <c r="F939" s="3"/>
     </row>
-    <row r="940" ht="15.75" customHeight="1">
+    <row r="940" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -8082,7 +8196,7 @@
       <c r="E940" s="3"/>
       <c r="F940" s="3"/>
     </row>
-    <row r="941" ht="15.75" customHeight="1">
+    <row r="941" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -8090,7 +8204,7 @@
       <c r="E941" s="3"/>
       <c r="F941" s="3"/>
     </row>
-    <row r="942" ht="15.75" customHeight="1">
+    <row r="942" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -8098,7 +8212,7 @@
       <c r="E942" s="3"/>
       <c r="F942" s="3"/>
     </row>
-    <row r="943" ht="15.75" customHeight="1">
+    <row r="943" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -8106,7 +8220,7 @@
       <c r="E943" s="3"/>
       <c r="F943" s="3"/>
     </row>
-    <row r="944" ht="15.75" customHeight="1">
+    <row r="944" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -8114,7 +8228,7 @@
       <c r="E944" s="3"/>
       <c r="F944" s="3"/>
     </row>
-    <row r="945" ht="15.75" customHeight="1">
+    <row r="945" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -8122,7 +8236,7 @@
       <c r="E945" s="3"/>
       <c r="F945" s="3"/>
     </row>
-    <row r="946" ht="15.75" customHeight="1">
+    <row r="946" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -8130,7 +8244,7 @@
       <c r="E946" s="3"/>
       <c r="F946" s="3"/>
     </row>
-    <row r="947" ht="15.75" customHeight="1">
+    <row r="947" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -8138,7 +8252,7 @@
       <c r="E947" s="3"/>
       <c r="F947" s="3"/>
     </row>
-    <row r="948" ht="15.75" customHeight="1">
+    <row r="948" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -8146,7 +8260,7 @@
       <c r="E948" s="3"/>
       <c r="F948" s="3"/>
     </row>
-    <row r="949" ht="15.75" customHeight="1">
+    <row r="949" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -8154,7 +8268,7 @@
       <c r="E949" s="3"/>
       <c r="F949" s="3"/>
     </row>
-    <row r="950" ht="15.75" customHeight="1">
+    <row r="950" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -8162,7 +8276,7 @@
       <c r="E950" s="3"/>
       <c r="F950" s="3"/>
     </row>
-    <row r="951" ht="15.75" customHeight="1">
+    <row r="951" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -8170,7 +8284,7 @@
       <c r="E951" s="3"/>
       <c r="F951" s="3"/>
     </row>
-    <row r="952" ht="15.75" customHeight="1">
+    <row r="952" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -8178,7 +8292,7 @@
       <c r="E952" s="3"/>
       <c r="F952" s="3"/>
     </row>
-    <row r="953" ht="15.75" customHeight="1">
+    <row r="953" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -8186,7 +8300,7 @@
       <c r="E953" s="3"/>
       <c r="F953" s="3"/>
     </row>
-    <row r="954" ht="15.75" customHeight="1">
+    <row r="954" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -8194,7 +8308,7 @@
       <c r="E954" s="3"/>
       <c r="F954" s="3"/>
     </row>
-    <row r="955" ht="15.75" customHeight="1">
+    <row r="955" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -8202,7 +8316,7 @@
       <c r="E955" s="3"/>
       <c r="F955" s="3"/>
     </row>
-    <row r="956" ht="15.75" customHeight="1">
+    <row r="956" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -8210,7 +8324,7 @@
       <c r="E956" s="3"/>
       <c r="F956" s="3"/>
     </row>
-    <row r="957" ht="15.75" customHeight="1">
+    <row r="957" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -8218,7 +8332,7 @@
       <c r="E957" s="3"/>
       <c r="F957" s="3"/>
     </row>
-    <row r="958" ht="15.75" customHeight="1">
+    <row r="958" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -8226,7 +8340,7 @@
       <c r="E958" s="3"/>
       <c r="F958" s="3"/>
     </row>
-    <row r="959" ht="15.75" customHeight="1">
+    <row r="959" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A959" s="3"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
@@ -8234,7 +8348,7 @@
       <c r="E959" s="3"/>
       <c r="F959" s="3"/>
     </row>
-    <row r="960" ht="15.75" customHeight="1">
+    <row r="960" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A960" s="3"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
@@ -8242,7 +8356,7 @@
       <c r="E960" s="3"/>
       <c r="F960" s="3"/>
     </row>
-    <row r="961" ht="15.75" customHeight="1">
+    <row r="961" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A961" s="3"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
@@ -8250,7 +8364,7 @@
       <c r="E961" s="3"/>
       <c r="F961" s="3"/>
     </row>
-    <row r="962" ht="15.75" customHeight="1">
+    <row r="962" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A962" s="3"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
@@ -8258,7 +8372,7 @@
       <c r="E962" s="3"/>
       <c r="F962" s="3"/>
     </row>
-    <row r="963" ht="15.75" customHeight="1">
+    <row r="963" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A963" s="3"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
@@ -8266,7 +8380,7 @@
       <c r="E963" s="3"/>
       <c r="F963" s="3"/>
     </row>
-    <row r="964" ht="15.75" customHeight="1">
+    <row r="964" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A964" s="3"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
@@ -8274,7 +8388,7 @@
       <c r="E964" s="3"/>
       <c r="F964" s="3"/>
     </row>
-    <row r="965" ht="15.75" customHeight="1">
+    <row r="965" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A965" s="3"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
@@ -8282,7 +8396,7 @@
       <c r="E965" s="3"/>
       <c r="F965" s="3"/>
     </row>
-    <row r="966" ht="15.75" customHeight="1">
+    <row r="966" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A966" s="3"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
@@ -8290,7 +8404,7 @@
       <c r="E966" s="3"/>
       <c r="F966" s="3"/>
     </row>
-    <row r="967" ht="15.75" customHeight="1">
+    <row r="967" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A967" s="3"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
@@ -8298,7 +8412,7 @@
       <c r="E967" s="3"/>
       <c r="F967" s="3"/>
     </row>
-    <row r="968" ht="15.75" customHeight="1">
+    <row r="968" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A968" s="3"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
@@ -8306,7 +8420,7 @@
       <c r="E968" s="3"/>
       <c r="F968" s="3"/>
     </row>
-    <row r="969" ht="15.75" customHeight="1">
+    <row r="969" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A969" s="3"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
@@ -8314,7 +8428,7 @@
       <c r="E969" s="3"/>
       <c r="F969" s="3"/>
     </row>
-    <row r="970" ht="15.75" customHeight="1">
+    <row r="970" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A970" s="3"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
@@ -8322,7 +8436,7 @@
       <c r="E970" s="3"/>
       <c r="F970" s="3"/>
     </row>
-    <row r="971" ht="15.75" customHeight="1">
+    <row r="971" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A971" s="3"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
@@ -8330,7 +8444,7 @@
       <c r="E971" s="3"/>
       <c r="F971" s="3"/>
     </row>
-    <row r="972" ht="15.75" customHeight="1">
+    <row r="972" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A972" s="3"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
@@ -8338,7 +8452,7 @@
       <c r="E972" s="3"/>
       <c r="F972" s="3"/>
     </row>
-    <row r="973" ht="15.75" customHeight="1">
+    <row r="973" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A973" s="3"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
@@ -8346,7 +8460,7 @@
       <c r="E973" s="3"/>
       <c r="F973" s="3"/>
     </row>
-    <row r="974" ht="15.75" customHeight="1">
+    <row r="974" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A974" s="3"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
@@ -8354,7 +8468,7 @@
       <c r="E974" s="3"/>
       <c r="F974" s="3"/>
     </row>
-    <row r="975" ht="15.75" customHeight="1">
+    <row r="975" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A975" s="3"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
@@ -8362,7 +8476,7 @@
       <c r="E975" s="3"/>
       <c r="F975" s="3"/>
     </row>
-    <row r="976" ht="15.75" customHeight="1">
+    <row r="976" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A976" s="3"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
@@ -8370,7 +8484,7 @@
       <c r="E976" s="3"/>
       <c r="F976" s="3"/>
     </row>
-    <row r="977" ht="15.75" customHeight="1">
+    <row r="977" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A977" s="3"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
@@ -8378,7 +8492,7 @@
       <c r="E977" s="3"/>
       <c r="F977" s="3"/>
     </row>
-    <row r="978" ht="15.75" customHeight="1">
+    <row r="978" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A978" s="3"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
@@ -8386,7 +8500,7 @@
       <c r="E978" s="3"/>
       <c r="F978" s="3"/>
     </row>
-    <row r="979" ht="15.75" customHeight="1">
+    <row r="979" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A979" s="3"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
@@ -8394,7 +8508,7 @@
       <c r="E979" s="3"/>
       <c r="F979" s="3"/>
     </row>
-    <row r="980" ht="15.75" customHeight="1">
+    <row r="980" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A980" s="3"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
@@ -8402,7 +8516,7 @@
       <c r="E980" s="3"/>
       <c r="F980" s="3"/>
     </row>
-    <row r="981" ht="15.75" customHeight="1">
+    <row r="981" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A981" s="3"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
@@ -8410,7 +8524,7 @@
       <c r="E981" s="3"/>
       <c r="F981" s="3"/>
     </row>
-    <row r="982" ht="15.75" customHeight="1">
+    <row r="982" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A982" s="3"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
@@ -8418,7 +8532,7 @@
       <c r="E982" s="3"/>
       <c r="F982" s="3"/>
     </row>
-    <row r="983" ht="15.75" customHeight="1">
+    <row r="983" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A983" s="3"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
@@ -8426,7 +8540,7 @@
       <c r="E983" s="3"/>
       <c r="F983" s="3"/>
     </row>
-    <row r="984" ht="15.75" customHeight="1">
+    <row r="984" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A984" s="3"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
@@ -8434,7 +8548,7 @@
       <c r="E984" s="3"/>
       <c r="F984" s="3"/>
     </row>
-    <row r="985" ht="15.75" customHeight="1">
+    <row r="985" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A985" s="3"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
@@ -8442,7 +8556,7 @@
       <c r="E985" s="3"/>
       <c r="F985" s="3"/>
     </row>
-    <row r="986" ht="15.75" customHeight="1">
+    <row r="986" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A986" s="3"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
@@ -8450,7 +8564,7 @@
       <c r="E986" s="3"/>
       <c r="F986" s="3"/>
     </row>
-    <row r="987" ht="15.75" customHeight="1">
+    <row r="987" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A987" s="3"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
@@ -8458,7 +8572,7 @@
       <c r="E987" s="3"/>
       <c r="F987" s="3"/>
     </row>
-    <row r="988" ht="15.75" customHeight="1">
+    <row r="988" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A988" s="3"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
@@ -8466,7 +8580,7 @@
       <c r="E988" s="3"/>
       <c r="F988" s="3"/>
     </row>
-    <row r="989" ht="15.75" customHeight="1">
+    <row r="989" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A989" s="3"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
@@ -8474,7 +8588,7 @@
       <c r="E989" s="3"/>
       <c r="F989" s="3"/>
     </row>
-    <row r="990" ht="15.75" customHeight="1">
+    <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A990" s="3"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
@@ -8482,7 +8596,7 @@
       <c r="E990" s="3"/>
       <c r="F990" s="3"/>
     </row>
-    <row r="991" ht="15.75" customHeight="1">
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A991" s="3"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
@@ -8490,7 +8604,7 @@
       <c r="E991" s="3"/>
       <c r="F991" s="3"/>
     </row>
-    <row r="992" ht="15.75" customHeight="1">
+    <row r="992" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A992" s="3"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
@@ -8498,7 +8612,7 @@
       <c r="E992" s="3"/>
       <c r="F992" s="3"/>
     </row>
-    <row r="993" ht="15.75" customHeight="1">
+    <row r="993" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A993" s="3"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
@@ -8506,7 +8620,7 @@
       <c r="E993" s="3"/>
       <c r="F993" s="3"/>
     </row>
-    <row r="994" ht="15.75" customHeight="1">
+    <row r="994" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A994" s="3"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
@@ -8514,7 +8628,7 @@
       <c r="E994" s="3"/>
       <c r="F994" s="3"/>
     </row>
-    <row r="995" ht="15.75" customHeight="1">
+    <row r="995" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A995" s="3"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
@@ -8522,7 +8636,7 @@
       <c r="E995" s="3"/>
       <c r="F995" s="3"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
+    <row r="996" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A996" s="3"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
@@ -8530,7 +8644,7 @@
       <c r="E996" s="3"/>
       <c r="F996" s="3"/>
     </row>
-    <row r="997" ht="15.75" customHeight="1">
+    <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A997" s="3"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
@@ -8538,7 +8652,7 @@
       <c r="E997" s="3"/>
       <c r="F997" s="3"/>
     </row>
-    <row r="998" ht="15.75" customHeight="1">
+    <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A998" s="3"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
@@ -8546,7 +8660,7 @@
       <c r="E998" s="3"/>
       <c r="F998" s="3"/>
     </row>
-    <row r="999" ht="15.75" customHeight="1">
+    <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A999" s="3"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
@@ -8554,7 +8668,7 @@
       <c r="E999" s="3"/>
       <c r="F999" s="3"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1000" s="3"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
@@ -8563,10 +8677,14 @@
       <c r="F1000" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$F$17"/>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <autoFilter ref="A1:F17"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>